--- a/assets/temp.xlsx
+++ b/assets/temp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23426"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jared\source\repos\avtopia\data_sync_desktop\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E85BFB0-4244-4BB2-A329-035970007BAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD435383-ECC9-434E-B688-5DE109EEBA25}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21330" yWindow="0" windowWidth="20655" windowHeight="15600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="1649">
   <si>
     <t>ID</t>
   </si>
@@ -197,7 +197,7 @@
     <t>Palm Beach Aircraft Service Inc.</t>
   </si>
   <si>
-    <t>2633 Lantana Rd </t>
+    <t>2633 Lantana Rd</t>
   </si>
   <si>
     <t>Suite 41</t>
@@ -863,7 +863,7 @@
     <t>Purvis Brothers Inc.</t>
   </si>
   <si>
-    <t>PO Box 957321 </t>
+    <t>PO Box 957321</t>
   </si>
   <si>
     <t>Mars Valencia Rd</t>
@@ -1721,7 +1721,7 @@
     <t>Shoals Flight Center/ NW Alabama Reg. Arprt</t>
   </si>
   <si>
-    <t>1729 T Ed Campbell Dr </t>
+    <t>1729 T Ed Campbell Dr</t>
   </si>
   <si>
     <t>Suite A</t>
@@ -1760,7 +1760,7 @@
     <t>Siam Land Flying</t>
   </si>
   <si>
-    <t>222 Don Mueang International Airport Office </t>
+    <t>222 Don Mueang International Airport Office</t>
   </si>
   <si>
     <t>Vibhavadi Rangsit Road Sanambin Don Mueang</t>
@@ -1904,7 +1904,7 @@
     <t>Sky Harbor Aviation</t>
   </si>
   <si>
-    <t>855 Saint Johns Bluff Rd N </t>
+    <t>855 Saint Johns Bluff Rd N</t>
   </si>
   <si>
     <t>Hangar 5</t>
@@ -3395,7 +3395,7 @@
     <t>Thro Avation (Zen Flight)</t>
   </si>
   <si>
-    <t>1000 New Highway </t>
+    <t>1000 New Highway</t>
   </si>
   <si>
     <t>Hangar #81</t>
@@ -3530,7 +3530,7 @@
     <t>Top Flight Detail</t>
   </si>
   <si>
-    <t>Mobile Regional Airport </t>
+    <t>Mobile Regional Airport</t>
   </si>
   <si>
     <t>371 Flave Pierce Road</t>
@@ -3764,7 +3764,7 @@
     <t>Tucson Aeroservice Center, Inc.</t>
   </si>
   <si>
-    <t>11700 W Avra Valley Rd </t>
+    <t>11700 W Avra Valley Rd</t>
   </si>
   <si>
     <t>Unit 85</t>
@@ -3905,7 +3905,7 @@
     <t>University of North Dakota, UND Aerospace Division</t>
   </si>
   <si>
-    <t>2798 Airport Dr </t>
+    <t>2798 Airport Dr</t>
   </si>
   <si>
     <t>Stop 9052</t>
@@ -4454,7 +4454,7 @@
     <t>West Houston Airport</t>
   </si>
   <si>
-    <t>PO Box 941789 </t>
+    <t>PO Box 941789</t>
   </si>
   <si>
     <t>18000 Groeschke Rd</t>
@@ -4970,16 +4970,22 @@
     <t>Google:Longitude</t>
   </si>
   <si>
-    <t>Executive Air</t>
+    <t>X</t>
+  </si>
+  <si>
+    <t>{"business_status":"OPERATIONAL","formatted_address":"2633 Lantana Rd #41, Lantana, FL 33462, USA","geometry":{"location":{"lat":26.5891232,"lng":-80.085217},"viewport":{"northeast":{"lat":26.5903062802915,"lng":-80.08379641970849},"southwest":{"lat":26.5876083197085,"lng":-80.0864943802915}}},"icon":"https://maps.gstatic.com/mapfiles/place_api/icons/v1/png_71/generic_business-71.png","name":"Palm Beach Aircraft Services Inc","place_id":"ChIJ4S0GlInY2IgRuTZrggV5fA0","plus_code":{"compound_code":"HWQ7+JW Lantana, FL, USA","global_code":"76RXHWQ7+JW"},"types":["point_of_interest","establishment"]}</t>
+  </si>
+  <si>
+    <t>Palm Beach Aircraft Services Inc</t>
   </si>
   <si>
     <t>OPERATIONAL</t>
   </si>
   <si>
-    <t>ChIJ43oI8gD5AogRU3iIWdpibqI</t>
-  </si>
-  <si>
-    <t>2131 Airport Dr, Green Bay, WI 54313, USA</t>
+    <t>ChIJ4S0GlInY2IgRuTZrggV5fA0</t>
+  </si>
+  <si>
+    <t>2633 Lantana Rd #41, Lantana, FL 33462, USA</t>
   </si>
 </sst>
 </file>
@@ -14307,7 +14313,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{478346B4-F175-45F8-959F-E74CD3C87AD8}">
-  <dimension ref="A1:Y263"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3"/>
@@ -14325,7 +14331,7 @@
     <col min="14" max="14" width="23.875" style="3" customWidth="1"/>
     <col min="15" max="15" width="23.875" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="23.875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="255.625" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
@@ -14431,24 +14437,6 @@
       <c r="L2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="T2" t="s">
-        <v>1643</v>
-      </c>
-      <c r="U2" t="s">
-        <v>1644</v>
-      </c>
-      <c r="V2" t="s">
-        <v>1645</v>
-      </c>
-      <c r="W2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="X2">
-        <v>44.4936934</v>
-      </c>
-      <c r="Y2">
-        <v>-88.1296081</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -14478,23 +14466,29 @@
       <c r="L3" s="5" t="s">
         <v>57</v>
       </c>
+      <c r="O3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>1644</v>
+      </c>
       <c r="T3" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="U3" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="V3" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="W3" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="X3">
-        <v>44.4936934</v>
+        <v>26.5891232</v>
       </c>
       <c r="Y3">
-        <v>-88.1296081</v>
+        <v>-80.085217</v>
       </c>
     </row>
     <row r="4">
@@ -14525,24 +14519,6 @@
       <c r="M4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="T4" t="s">
-        <v>1643</v>
-      </c>
-      <c r="U4" t="s">
-        <v>1644</v>
-      </c>
-      <c r="V4" t="s">
-        <v>1645</v>
-      </c>
-      <c r="W4" t="s">
-        <v>1646</v>
-      </c>
-      <c r="X4">
-        <v>44.4936934</v>
-      </c>
-      <c r="Y4">
-        <v>-88.1296081</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -14572,24 +14548,6 @@
       <c r="M5" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="T5" t="s">
-        <v>1643</v>
-      </c>
-      <c r="U5" t="s">
-        <v>1644</v>
-      </c>
-      <c r="V5" t="s">
-        <v>1645</v>
-      </c>
-      <c r="W5" t="s">
-        <v>1646</v>
-      </c>
-      <c r="X5">
-        <v>44.4936934</v>
-      </c>
-      <c r="Y5">
-        <v>-88.1296081</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -14615,24 +14573,6 @@
       </c>
       <c r="L6" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="T6" t="s">
-        <v>1643</v>
-      </c>
-      <c r="U6" t="s">
-        <v>1644</v>
-      </c>
-      <c r="V6" t="s">
-        <v>1645</v>
-      </c>
-      <c r="W6" t="s">
-        <v>1646</v>
-      </c>
-      <c r="X6">
-        <v>44.4936934</v>
-      </c>
-      <c r="Y6">
-        <v>-88.1296081</v>
       </c>
     </row>
   </sheetData>

--- a/assets/temp.xlsx
+++ b/assets/temp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23530"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jared\source\repos\avtopia\data_sync_desktop\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43D3B13-EF51-4DCC-A044-B7A0A2CAC847}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00966F7-72DB-44E1-86E6-BD3D49187CAF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7288" uniqueCount="2848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7572" uniqueCount="2849">
   <si>
     <t>ID</t>
   </si>
@@ -5040,6 +5040,9 @@
   </si>
   <si>
     <t>1005 Sycolin Rd Suite 106, Leesburg, VA 20175, United States</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t/>
@@ -17943,7 +17946,7 @@
   <dimension ref="A1:AD264"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="3"/>
+    <col min="1" max="1" width="0" style="3" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="31.125" style="24" customWidth="1"/>
     <col min="3" max="3" width="23.5" style="3" hidden="1" customWidth="1"/>
     <col min="4" max="5" width="12.5" style="3" hidden="1" customWidth="1"/>
@@ -17952,14 +17955,14 @@
     <col min="8" max="8" width="13.625" style="3" customWidth="1"/>
     <col min="9" max="9" width="5.125" style="3" customWidth="1"/>
     <col min="10" max="10" width="11.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="23.5" style="3" customWidth="1"/>
-    <col min="13" max="13" width="55.125" style="3" customWidth="1"/>
-    <col min="14" max="19" width="23.875" style="3" customWidth="1"/>
-    <col min="20" max="20" width="57.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="3" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5" style="3" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="55.125" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="19" width="23.875" style="3" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="57.625" style="3" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="28.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.875" style="3" customWidth="1"/>
-    <col min="23" max="23" width="26.25" style="3" customWidth="1"/>
+    <col min="22" max="22" width="20.875" style="3" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="26.25" style="3" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="40.125" style="3" bestFit="1" customWidth="1"/>
     <col min="25" max="28" width="9.625" style="3" customWidth="1"/>
     <col min="29" max="29" width="15" style="3" bestFit="1" customWidth="1"/>
@@ -18108,16 +18111,16 @@
       <c r="X2" t="s">
         <v>1656</v>
       </c>
-      <c r="Y2" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z2" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB2" s="26" t="s">
+      <c r="Y2" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z2" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA2" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB2" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC2">
@@ -18250,6 +18253,9 @@
       <c r="X4" t="s">
         <v>1666</v>
       </c>
+      <c r="Y4" s="26" t="s">
+        <v>1667</v>
+      </c>
       <c r="Z4" s="27" t="s">
         <v>1650</v>
       </c>
@@ -18298,28 +18304,40 @@
         <v>1649</v>
       </c>
       <c r="P5" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="Q5" t="s">
         <v>1650</v>
       </c>
       <c r="S5" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="T5" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="U5" s="26" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="V5" t="s">
         <v>1654</v>
       </c>
       <c r="W5" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="X5" t="s">
-        <v>1672</v>
+        <v>1673</v>
+      </c>
+      <c r="Y5" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z5" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA5" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB5" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC5">
         <v>46.929774999999999</v>
@@ -18360,22 +18378,25 @@
         <v>1650</v>
       </c>
       <c r="S6" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="T6" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="U6" s="27" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="V6" t="s">
         <v>1654</v>
       </c>
       <c r="W6" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="X6" t="s">
-        <v>1677</v>
+        <v>1678</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z6" s="27" t="s">
         <v>1650</v>
@@ -18425,10 +18446,10 @@
         <v>1650</v>
       </c>
       <c r="S7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="T7" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="U7" s="27" t="s">
         <v>80</v>
@@ -18437,10 +18458,13 @@
         <v>1654</v>
       </c>
       <c r="W7" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="X7" t="s">
-        <v>1681</v>
+        <v>1682</v>
+      </c>
+      <c r="Y7" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z7" s="27" t="s">
         <v>1650</v>
@@ -18493,22 +18517,25 @@
         <v>1650</v>
       </c>
       <c r="S8" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="T8" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="U8" s="27" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="V8" t="s">
         <v>1654</v>
       </c>
       <c r="W8" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="X8" t="s">
-        <v>1686</v>
+        <v>1687</v>
+      </c>
+      <c r="Y8" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z8" s="27" t="s">
         <v>1650</v>
@@ -18564,22 +18591,22 @@
         <v>1650</v>
       </c>
       <c r="S9" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="T9" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="U9" s="27" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="V9" t="s">
         <v>1654</v>
       </c>
       <c r="W9" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="X9" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="Y9" s="27" t="s">
         <v>1650</v>
@@ -18638,28 +18665,34 @@
         <v>1650</v>
       </c>
       <c r="S10" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="T10" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="U10" s="27" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="V10" t="s">
         <v>1654</v>
       </c>
       <c r="W10" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="X10" t="s">
-        <v>1696</v>
+        <v>1697</v>
+      </c>
+      <c r="Y10" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z10" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA10" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB10" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC10">
         <v>36.748237899999999</v>
@@ -18703,22 +18736,22 @@
         <v>1650</v>
       </c>
       <c r="S11" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="T11" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="U11" s="27" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="V11" t="s">
         <v>1654</v>
       </c>
       <c r="W11" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="X11" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="Y11" s="27" t="s">
         <v>1650</v>
@@ -18774,22 +18807,22 @@
         <v>1650</v>
       </c>
       <c r="S12" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="T12" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="U12" s="27" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="V12" t="s">
         <v>1654</v>
       </c>
       <c r="W12" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="X12" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="Y12" s="27" t="s">
         <v>1650</v>
@@ -18845,22 +18878,22 @@
         <v>1650</v>
       </c>
       <c r="S13" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="T13" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="U13" s="27" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="V13" t="s">
         <v>1654</v>
       </c>
       <c r="W13" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="X13" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="Y13" s="27" t="s">
         <v>1650</v>
@@ -18916,22 +18949,25 @@
         <v>1650</v>
       </c>
       <c r="S14" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="T14" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="U14" s="27" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="V14" t="s">
         <v>1654</v>
       </c>
       <c r="W14" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="X14" t="s">
-        <v>1716</v>
+        <v>1717</v>
+      </c>
+      <c r="Y14" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z14" s="27" t="s">
         <v>1650</v>
@@ -18984,22 +19020,34 @@
         <v>1650</v>
       </c>
       <c r="S15" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="T15" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="U15" s="26" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="V15" t="s">
         <v>1654</v>
       </c>
       <c r="W15" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="X15" t="s">
-        <v>1721</v>
+        <v>1722</v>
+      </c>
+      <c r="Y15" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z15" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA15" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB15" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC15">
         <v>18.465774400000001</v>
@@ -19043,22 +19091,22 @@
         <v>1650</v>
       </c>
       <c r="S16" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="T16" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="U16" s="27" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="V16" t="s">
         <v>1654</v>
       </c>
       <c r="W16" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="X16" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="Y16" s="27" t="s">
         <v>1650</v>
@@ -19111,10 +19159,10 @@
         <v>1650</v>
       </c>
       <c r="S17" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="T17" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="U17" s="27" t="s">
         <v>156</v>
@@ -19123,13 +19171,22 @@
         <v>1654</v>
       </c>
       <c r="W17" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="X17" t="s">
-        <v>1730</v>
+        <v>1731</v>
+      </c>
+      <c r="Y17" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z17" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA17" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB17" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC17">
         <v>34.131035300000001</v>
@@ -19173,22 +19230,22 @@
         <v>1650</v>
       </c>
       <c r="S18" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="T18" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="U18" s="27" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="V18" t="s">
         <v>1654</v>
       </c>
       <c r="W18" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="X18" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="Y18" s="27" t="s">
         <v>1650</v>
@@ -19241,22 +19298,25 @@
         <v>1650</v>
       </c>
       <c r="S19" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="T19" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="U19" s="27" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="V19" t="s">
         <v>1654</v>
       </c>
       <c r="W19" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="X19" t="s">
-        <v>1740</v>
+        <v>1741</v>
+      </c>
+      <c r="Y19" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z19" s="27" t="s">
         <v>1650</v>
@@ -19309,22 +19369,25 @@
         <v>1650</v>
       </c>
       <c r="S20" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="T20" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="U20" s="27" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="V20" t="s">
         <v>1654</v>
       </c>
       <c r="W20" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="X20" t="s">
-        <v>1745</v>
+        <v>1746</v>
+      </c>
+      <c r="Y20" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z20" s="27" t="s">
         <v>1650</v>
@@ -19377,22 +19440,22 @@
         <v>1650</v>
       </c>
       <c r="S21" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="T21" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="U21" s="27" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="V21" t="s">
         <v>1654</v>
       </c>
       <c r="W21" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="X21" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="Y21" s="27" t="s">
         <v>1650</v>
@@ -19445,10 +19508,10 @@
         <v>1650</v>
       </c>
       <c r="S22" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="T22" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="U22" s="27" t="s">
         <v>187</v>
@@ -19457,10 +19520,13 @@
         <v>1654</v>
       </c>
       <c r="W22" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="X22" t="s">
-        <v>1754</v>
+        <v>1755</v>
+      </c>
+      <c r="Y22" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z22" s="27" t="s">
         <v>1650</v>
@@ -19516,22 +19582,22 @@
         <v>1650</v>
       </c>
       <c r="S23" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="T23" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="U23" s="27" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="V23" t="s">
         <v>1654</v>
       </c>
       <c r="W23" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="X23" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="Y23" s="27" t="s">
         <v>1650</v>
@@ -19587,22 +19653,22 @@
         <v>1650</v>
       </c>
       <c r="S24" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="T24" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="U24" s="27" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="V24" t="s">
         <v>1654</v>
       </c>
       <c r="W24" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="X24" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="Y24" s="27" t="s">
         <v>1650</v>
@@ -19658,22 +19724,22 @@
         <v>1650</v>
       </c>
       <c r="S25" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="T25" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="U25" s="27" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="V25" t="s">
         <v>1654</v>
       </c>
       <c r="W25" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="X25" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="Y25" s="27" t="s">
         <v>1650</v>
@@ -19729,10 +19795,10 @@
         <v>1650</v>
       </c>
       <c r="S26" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="T26" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="U26" s="27" t="s">
         <v>212</v>
@@ -19741,10 +19807,22 @@
         <v>1654</v>
       </c>
       <c r="W26" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="X26" t="s">
-        <v>1773</v>
+        <v>1774</v>
+      </c>
+      <c r="Y26" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z26" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA26" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB26" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC26">
         <v>33.621678699999997</v>
@@ -19788,30 +19866,33 @@
         <v>1650</v>
       </c>
       <c r="S27" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="T27" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="U27" s="26" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="V27" t="s">
         <v>1654</v>
       </c>
       <c r="W27" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="X27" t="s">
-        <v>1778</v>
-      </c>
-      <c r="Y27" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA27" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB27" s="26" t="s">
+        <v>1779</v>
+      </c>
+      <c r="Y27" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z27" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA27" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB27" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC27">
@@ -19856,25 +19937,34 @@
         <v>1650</v>
       </c>
       <c r="S28" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="T28" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="U28" s="27" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="V28" t="s">
         <v>1654</v>
       </c>
       <c r="W28" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="X28" t="s">
-        <v>1783</v>
+        <v>1784</v>
+      </c>
+      <c r="Y28" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z28" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA28" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB28" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC28">
         <v>40.756764099999998</v>
@@ -19918,22 +20008,28 @@
         <v>1650</v>
       </c>
       <c r="S29" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="T29" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="U29" s="27" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="V29" t="s">
         <v>1654</v>
       </c>
       <c r="W29" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="X29" t="s">
-        <v>1788</v>
+        <v>1789</v>
+      </c>
+      <c r="Y29" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z29" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA29" s="27" t="s">
         <v>1650</v>
@@ -19983,22 +20079,22 @@
         <v>1650</v>
       </c>
       <c r="S30" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="T30" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="U30" s="27" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="V30" t="s">
         <v>1654</v>
       </c>
       <c r="W30" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="X30" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="Y30" s="27" t="s">
         <v>1650</v>
@@ -20057,22 +20153,34 @@
         <v>1650</v>
       </c>
       <c r="S31" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="T31" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="U31" s="27" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="V31" t="s">
         <v>1654</v>
       </c>
       <c r="W31" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="X31" t="s">
-        <v>1798</v>
+        <v>1799</v>
+      </c>
+      <c r="Y31" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z31" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA31" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB31" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC31">
         <v>64.805467399999998</v>
@@ -20116,10 +20224,10 @@
         <v>1650</v>
       </c>
       <c r="S32" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="T32" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="U32" s="27" t="s">
         <v>253</v>
@@ -20128,10 +20236,13 @@
         <v>1654</v>
       </c>
       <c r="W32" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="X32" t="s">
-        <v>1802</v>
+        <v>1803</v>
+      </c>
+      <c r="Y32" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z32" s="27" t="s">
         <v>1650</v>
@@ -20184,22 +20295,34 @@
         <v>1650</v>
       </c>
       <c r="S33" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="T33" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="U33" s="27" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="V33" t="s">
         <v>1654</v>
       </c>
       <c r="W33" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="X33" t="s">
-        <v>1807</v>
+        <v>1808</v>
+      </c>
+      <c r="Y33" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z33" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA33" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB33" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC33">
         <v>21.775877000000001</v>
@@ -20243,22 +20366,25 @@
         <v>1650</v>
       </c>
       <c r="S34" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="T34" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="U34" s="27" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="V34" t="s">
         <v>1654</v>
       </c>
       <c r="W34" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="X34" t="s">
-        <v>1812</v>
+        <v>1813</v>
+      </c>
+      <c r="Y34" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z34" s="27" t="s">
         <v>1650</v>
@@ -20314,22 +20440,22 @@
         <v>1650</v>
       </c>
       <c r="S35" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="T35" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="U35" s="27" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="V35" t="s">
         <v>1654</v>
       </c>
       <c r="W35" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="X35" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="Y35" s="27" t="s">
         <v>1650</v>
@@ -20382,10 +20508,10 @@
         <v>1650</v>
       </c>
       <c r="S36" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="T36" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="U36" s="27" t="s">
         <v>281</v>
@@ -20394,10 +20520,10 @@
         <v>1654</v>
       </c>
       <c r="W36" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="X36" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="Y36" s="27" t="s">
         <v>1650</v>
@@ -20453,22 +20579,34 @@
         <v>1650</v>
       </c>
       <c r="S37" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="T37" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="U37" s="26" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="V37" t="s">
         <v>1654</v>
       </c>
       <c r="W37" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="X37" t="s">
-        <v>1826</v>
+        <v>1827</v>
+      </c>
+      <c r="Y37" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z37" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA37" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB37" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC37">
         <v>41.336604999999999</v>
@@ -20538,22 +20676,25 @@
         <v>1650</v>
       </c>
       <c r="S39" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="T39" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="U39" s="27" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="V39" t="s">
         <v>1654</v>
       </c>
       <c r="W39" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="X39" t="s">
-        <v>1831</v>
+        <v>1832</v>
+      </c>
+      <c r="Y39" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z39" s="27" t="s">
         <v>1650</v>
@@ -20609,10 +20750,10 @@
         <v>1650</v>
       </c>
       <c r="S40" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="T40" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="U40" s="27" t="s">
         <v>308</v>
@@ -20621,10 +20762,10 @@
         <v>1654</v>
       </c>
       <c r="W40" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="X40" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="Y40" s="27" t="s">
         <v>1650</v>
@@ -20680,22 +20821,25 @@
         <v>1650</v>
       </c>
       <c r="S41" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="T41" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="U41" s="27" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="V41" t="s">
         <v>1654</v>
       </c>
       <c r="W41" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="X41" t="s">
-        <v>1840</v>
+        <v>1841</v>
+      </c>
+      <c r="Y41" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z41" s="27" t="s">
         <v>1650</v>
@@ -20745,22 +20889,22 @@
         <v>1650</v>
       </c>
       <c r="S42" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="T42" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="U42" s="27" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="V42" t="s">
         <v>1654</v>
       </c>
       <c r="W42" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="X42" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="Y42" s="27" t="s">
         <v>1650</v>
@@ -20816,22 +20960,25 @@
         <v>1650</v>
       </c>
       <c r="S43" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="T43" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="U43" s="27" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="V43" t="s">
         <v>1654</v>
       </c>
       <c r="W43" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="X43" t="s">
-        <v>1850</v>
+        <v>1851</v>
+      </c>
+      <c r="Y43" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z43" s="27" t="s">
         <v>1650</v>
@@ -20881,22 +21028,25 @@
         <v>1650</v>
       </c>
       <c r="S44" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="T44" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="U44" s="27" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="V44" t="s">
         <v>1654</v>
       </c>
       <c r="W44" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="X44" t="s">
-        <v>1855</v>
+        <v>1856</v>
+      </c>
+      <c r="Y44" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z44" s="27" t="s">
         <v>1650</v>
@@ -20946,10 +21096,10 @@
         <v>1650</v>
       </c>
       <c r="S45" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="T45" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="U45" s="27" t="s">
         <v>337</v>
@@ -20958,13 +21108,22 @@
         <v>1654</v>
       </c>
       <c r="W45" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="X45" t="s">
-        <v>1859</v>
+        <v>1860</v>
+      </c>
+      <c r="Y45" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z45" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AA45" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB45" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC45">
         <v>19.3328165</v>
@@ -21008,33 +21167,33 @@
         <v>1650</v>
       </c>
       <c r="S46" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="T46" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="U46" s="26" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="V46" t="s">
         <v>1654</v>
       </c>
       <c r="W46" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="X46" t="s">
-        <v>1864</v>
-      </c>
-      <c r="Y46" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z46" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA46" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB46" s="26" t="s">
+        <v>1865</v>
+      </c>
+      <c r="Y46" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z46" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA46" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB46" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC46">
@@ -21079,22 +21238,25 @@
         <v>1650</v>
       </c>
       <c r="S47" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="T47" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="U47" s="27" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="V47" t="s">
         <v>1654</v>
       </c>
       <c r="W47" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="X47" t="s">
-        <v>1869</v>
+        <v>1870</v>
+      </c>
+      <c r="Y47" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z47" s="27" t="s">
         <v>1650</v>
@@ -21147,22 +21309,22 @@
         <v>1650</v>
       </c>
       <c r="S48" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="T48" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="U48" s="27" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="V48" t="s">
         <v>1654</v>
       </c>
       <c r="W48" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="X48" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="Y48" s="27" t="s">
         <v>1650</v>
@@ -21218,22 +21380,25 @@
         <v>1650</v>
       </c>
       <c r="S49" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="T49" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="U49" s="27" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="V49" t="s">
         <v>1654</v>
       </c>
       <c r="W49" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="X49" t="s">
-        <v>1879</v>
+        <v>1880</v>
+      </c>
+      <c r="Y49" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z49" s="27" t="s">
         <v>1650</v>
@@ -21286,10 +21451,10 @@
         <v>1650</v>
       </c>
       <c r="S50" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="T50" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="U50" s="27" t="s">
         <v>368</v>
@@ -21298,10 +21463,10 @@
         <v>1654</v>
       </c>
       <c r="W50" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="X50" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="Y50" s="27" t="s">
         <v>1650</v>
@@ -21357,22 +21522,22 @@
         <v>1650</v>
       </c>
       <c r="S51" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="T51" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="U51" s="27" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="V51" t="s">
         <v>1654</v>
       </c>
       <c r="W51" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="X51" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="Y51" s="27" t="s">
         <v>1650</v>
@@ -21431,22 +21596,34 @@
         <v>1650</v>
       </c>
       <c r="S52" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="T52" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="U52" s="27" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="V52" t="s">
         <v>1654</v>
       </c>
       <c r="W52" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="X52" t="s">
-        <v>1893</v>
+        <v>1894</v>
+      </c>
+      <c r="Y52" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z52" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA52" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB52" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC52">
         <v>42.851202399999998</v>
@@ -21519,10 +21696,10 @@
         <v>1650</v>
       </c>
       <c r="S54" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="T54" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="U54" s="27" t="s">
         <v>393</v>
@@ -21531,10 +21708,13 @@
         <v>1654</v>
       </c>
       <c r="W54" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="X54" t="s">
-        <v>1897</v>
+        <v>1898</v>
+      </c>
+      <c r="Y54" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z54" s="27" t="s">
         <v>1650</v>
@@ -21584,25 +21764,34 @@
         <v>1650</v>
       </c>
       <c r="S55" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="T55" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="U55" s="26" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="V55" t="s">
         <v>1654</v>
       </c>
       <c r="W55" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="X55" t="s">
-        <v>1902</v>
-      </c>
-      <c r="AA55" s="26" t="s">
-        <v>1650</v>
+        <v>1903</v>
+      </c>
+      <c r="Y55" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z55" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA55" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB55" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC55">
         <v>26.85333</v>
@@ -21649,22 +21838,22 @@
         <v>1650</v>
       </c>
       <c r="S56" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="T56" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="U56" s="27" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="V56" t="s">
         <v>1654</v>
       </c>
       <c r="W56" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="X56" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="Y56" s="27" t="s">
         <v>1650</v>
@@ -21723,25 +21912,34 @@
         <v>1650</v>
       </c>
       <c r="S57" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="T57" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="U57" s="27" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="V57" t="s">
         <v>1654</v>
       </c>
       <c r="W57" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="X57" t="s">
-        <v>1912</v>
+        <v>1913</v>
+      </c>
+      <c r="Y57" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z57" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA57" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB57" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC57">
         <v>42.293901499999997</v>
@@ -21785,33 +21983,33 @@
         <v>1650</v>
       </c>
       <c r="S58" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="T58" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="U58" s="26" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="V58" t="s">
         <v>1654</v>
       </c>
       <c r="W58" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="X58" t="s">
-        <v>1917</v>
-      </c>
-      <c r="Y58" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z58" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA58" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB58" s="26" t="s">
+        <v>1918</v>
+      </c>
+      <c r="Y58" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z58" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA58" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB58" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC58">
@@ -21856,25 +22054,34 @@
         <v>1650</v>
       </c>
       <c r="S59" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="T59" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="U59" s="27" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="V59" t="s">
         <v>1654</v>
       </c>
       <c r="W59" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="X59" t="s">
-        <v>1922</v>
+        <v>1923</v>
+      </c>
+      <c r="Y59" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z59" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA59" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB59" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC59">
         <v>34.156554200000002</v>
@@ -21918,22 +22125,22 @@
         <v>1650</v>
       </c>
       <c r="S60" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="T60" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="U60" s="27" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="V60" t="s">
         <v>1654</v>
       </c>
       <c r="W60" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X60" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="Y60" s="27" t="s">
         <v>1650</v>
@@ -21986,22 +22193,34 @@
         <v>1650</v>
       </c>
       <c r="S61" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="T61" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="U61" s="26" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="V61" t="s">
         <v>1654</v>
       </c>
       <c r="W61" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="X61" t="s">
-        <v>1932</v>
+        <v>1933</v>
+      </c>
+      <c r="Y61" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z61" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA61" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB61" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC61">
         <v>42.228769000000007</v>
@@ -22042,22 +22261,22 @@
         <v>1650</v>
       </c>
       <c r="S62" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="T62" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="U62" s="27" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="V62" t="s">
         <v>1654</v>
       </c>
       <c r="W62" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="X62" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="Y62" s="27" t="s">
         <v>1650</v>
@@ -22104,13 +22323,13 @@
         <v>450</v>
       </c>
       <c r="N63" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="P63" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="S63" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="64" spans="1:30">
@@ -22148,22 +22367,22 @@
         <v>1650</v>
       </c>
       <c r="S64" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="T64" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="U64" s="27" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="V64" t="s">
         <v>1654</v>
       </c>
       <c r="W64" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="X64" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="Y64" s="27" t="s">
         <v>1650</v>
@@ -22219,22 +22438,22 @@
         <v>1650</v>
       </c>
       <c r="S65" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="T65" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="U65" s="27" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="V65" t="s">
         <v>1654</v>
       </c>
       <c r="W65" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="X65" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="Y65" s="27" t="s">
         <v>1650</v>
@@ -22290,28 +22509,34 @@
         <v>1650</v>
       </c>
       <c r="S66" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="T66" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="U66" s="27" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="V66" t="s">
         <v>1654</v>
       </c>
       <c r="W66" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="X66" t="s">
-        <v>1954</v>
+        <v>1955</v>
+      </c>
+      <c r="Y66" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z66" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA66" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB66" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC66">
         <v>47.102651999999999</v>
@@ -22355,28 +22580,34 @@
         <v>1650</v>
       </c>
       <c r="S67" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="T67" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="U67" s="27" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="V67" t="s">
         <v>1654</v>
       </c>
       <c r="W67" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="X67" t="s">
-        <v>1959</v>
+        <v>1960</v>
+      </c>
+      <c r="Y67" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z67" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA67" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB67" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC67">
         <v>41.451633000000001</v>
@@ -22420,28 +22651,34 @@
         <v>1650</v>
       </c>
       <c r="S68" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="T68" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="U68" s="27" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="V68" t="s">
         <v>1654</v>
       </c>
       <c r="W68" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="X68" t="s">
-        <v>1964</v>
+        <v>1965</v>
+      </c>
+      <c r="Y68" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z68" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA68" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB68" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC68">
         <v>34.898585199999999</v>
@@ -22485,22 +22722,34 @@
         <v>1650</v>
       </c>
       <c r="S69" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="T69" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="U69" s="27" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="V69" t="s">
         <v>1654</v>
       </c>
       <c r="W69" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="X69" t="s">
-        <v>1969</v>
+        <v>1970</v>
+      </c>
+      <c r="Y69" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z69" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA69" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB69" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC69">
         <v>37.963154099999997</v>
@@ -22544,22 +22793,22 @@
         <v>1650</v>
       </c>
       <c r="S70" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="T70" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="U70" s="27" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="V70" t="s">
         <v>1654</v>
       </c>
       <c r="W70" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="X70" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="Y70" s="27" t="s">
         <v>1650</v>
@@ -22615,25 +22864,34 @@
         <v>1650</v>
       </c>
       <c r="S71" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="T71" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="U71" s="26" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="V71" t="s">
         <v>1654</v>
       </c>
       <c r="W71" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="X71" t="s">
-        <v>1979</v>
-      </c>
-      <c r="AA71" s="26" t="s">
-        <v>1650</v>
+        <v>1980</v>
+      </c>
+      <c r="Y71" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z71" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA71" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB71" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC71">
         <v>35.5783293</v>
@@ -22674,22 +22932,25 @@
         <v>1650</v>
       </c>
       <c r="S72" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="T72" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="U72" s="27" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="V72" t="s">
         <v>1654</v>
       </c>
       <c r="W72" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="X72" t="s">
-        <v>1984</v>
+        <v>1985</v>
+      </c>
+      <c r="Y72" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z72" s="27" t="s">
         <v>1650</v>
@@ -22742,33 +23003,33 @@
         <v>1650</v>
       </c>
       <c r="S73" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="T73" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="U73" s="26" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="V73" t="s">
         <v>1654</v>
       </c>
       <c r="W73" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="X73" t="s">
-        <v>1989</v>
-      </c>
-      <c r="Y73" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z73" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA73" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB73" s="26" t="s">
+        <v>1990</v>
+      </c>
+      <c r="Y73" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z73" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA73" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB73" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC73">
@@ -22810,22 +23071,25 @@
         <v>1650</v>
       </c>
       <c r="S74" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="T74" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="U74" s="27" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="V74" t="s">
         <v>1654</v>
       </c>
       <c r="W74" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="X74" t="s">
-        <v>1994</v>
+        <v>1995</v>
+      </c>
+      <c r="Y74" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z74" s="27" t="s">
         <v>1650</v>
@@ -22878,10 +23142,10 @@
         <v>1650</v>
       </c>
       <c r="S75" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="T75" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="U75" s="27" t="s">
         <v>518</v>
@@ -22890,10 +23154,10 @@
         <v>1654</v>
       </c>
       <c r="W75" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="X75" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="Y75" s="27" t="s">
         <v>1650</v>
@@ -22949,30 +23213,33 @@
         <v>1650</v>
       </c>
       <c r="S76" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="T76" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="U76" s="26" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="V76" t="s">
         <v>1654</v>
       </c>
       <c r="W76" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="X76" t="s">
-        <v>2003</v>
-      </c>
-      <c r="Z76" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA76" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB76" s="26" t="s">
+        <v>2004</v>
+      </c>
+      <c r="Y76" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z76" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA76" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB76" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC76">
@@ -23014,22 +23281,34 @@
         <v>1650</v>
       </c>
       <c r="S77" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="T77" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="U77" s="26" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="V77" t="s">
         <v>1654</v>
       </c>
       <c r="W77" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="X77" t="s">
-        <v>2008</v>
+        <v>2009</v>
+      </c>
+      <c r="Y77" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z77" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA77" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB77" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC77">
         <v>45.455509999999997</v>
@@ -23076,22 +23355,22 @@
         <v>1650</v>
       </c>
       <c r="S78" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="T78" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="U78" s="27" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="V78" t="s">
         <v>1654</v>
       </c>
       <c r="W78" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="X78" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="Y78" s="27" t="s">
         <v>1650</v>
@@ -23147,22 +23426,25 @@
         <v>1650</v>
       </c>
       <c r="S79" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="T79" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="U79" s="27" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="V79" t="s">
         <v>1654</v>
       </c>
       <c r="W79" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="X79" t="s">
-        <v>2018</v>
+        <v>2019</v>
+      </c>
+      <c r="Y79" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z79" s="27" t="s">
         <v>1650</v>
@@ -23212,10 +23494,10 @@
         <v>1650</v>
       </c>
       <c r="S80" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="T80" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="U80" s="27" t="s">
         <v>546</v>
@@ -23224,10 +23506,13 @@
         <v>1654</v>
       </c>
       <c r="W80" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="X80" t="s">
-        <v>2022</v>
+        <v>2023</v>
+      </c>
+      <c r="Y80" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z80" s="27" t="s">
         <v>1650</v>
@@ -23277,22 +23562,25 @@
         <v>1650</v>
       </c>
       <c r="S81" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="T81" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="U81" s="27" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="V81" t="s">
         <v>1654</v>
       </c>
       <c r="W81" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="X81" t="s">
-        <v>2027</v>
+        <v>2028</v>
+      </c>
+      <c r="Y81" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z81" s="27" t="s">
         <v>1650</v>
@@ -23348,22 +23636,22 @@
         <v>1650</v>
       </c>
       <c r="S82" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="T82" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="U82" s="27" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="V82" t="s">
         <v>1654</v>
       </c>
       <c r="W82" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="X82" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Y82" s="27" t="s">
         <v>1650</v>
@@ -23419,22 +23707,25 @@
         <v>1650</v>
       </c>
       <c r="S83" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="T83" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="U83" s="27" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="V83" t="s">
         <v>1654</v>
       </c>
       <c r="W83" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="X83" t="s">
-        <v>2037</v>
+        <v>2038</v>
+      </c>
+      <c r="Y83" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z83" s="27" t="s">
         <v>1650</v>
@@ -23487,25 +23778,31 @@
         <v>1650</v>
       </c>
       <c r="S84" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="T84" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="U84" s="27" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="V84" t="s">
         <v>1654</v>
       </c>
       <c r="W84" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="X84" t="s">
-        <v>2042</v>
+        <v>2043</v>
+      </c>
+      <c r="Y84" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z84" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AA84" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AB84" s="27" t="s">
         <v>1650</v>
@@ -23549,22 +23846,28 @@
         <v>1650</v>
       </c>
       <c r="S85" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="T85" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="U85" s="27" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="V85" t="s">
         <v>1654</v>
       </c>
       <c r="W85" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="X85" t="s">
-        <v>2047</v>
+        <v>2048</v>
+      </c>
+      <c r="Y85" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z85" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA85" s="27" t="s">
         <v>1650</v>
@@ -23617,22 +23920,25 @@
         <v>1650</v>
       </c>
       <c r="S86" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="T86" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="U86" s="27" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="V86" t="s">
         <v>1654</v>
       </c>
       <c r="W86" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="X86" t="s">
-        <v>2052</v>
+        <v>2053</v>
+      </c>
+      <c r="Y86" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z86" s="27" t="s">
         <v>1650</v>
@@ -23685,22 +23991,22 @@
         <v>1650</v>
       </c>
       <c r="S87" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="T87" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="U87" s="27" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="V87" t="s">
         <v>1654</v>
       </c>
       <c r="W87" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="X87" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="Y87" s="27" t="s">
         <v>1650</v>
@@ -23759,25 +24065,34 @@
         <v>1650</v>
       </c>
       <c r="S88" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="T88" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="U88" s="26" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="V88" t="s">
         <v>1654</v>
       </c>
       <c r="W88" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="X88" t="s">
-        <v>2062</v>
-      </c>
-      <c r="AA88" s="26" t="s">
-        <v>1650</v>
+        <v>2063</v>
+      </c>
+      <c r="Y88" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z88" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA88" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB88" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC88">
         <v>42.972476700000001</v>
@@ -23821,28 +24136,31 @@
         <v>1650</v>
       </c>
       <c r="S89" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="T89" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="U89" s="27" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="V89" t="s">
         <v>1654</v>
       </c>
       <c r="W89" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="X89" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="Y89" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="Z89" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AA89" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AB89" s="27" t="s">
         <v>1650</v>
@@ -23889,10 +24207,10 @@
         <v>1650</v>
       </c>
       <c r="S90" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="T90" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="U90" s="27" t="s">
         <v>614</v>
@@ -23901,10 +24219,13 @@
         <v>1654</v>
       </c>
       <c r="W90" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="X90" t="s">
-        <v>2071</v>
+        <v>2072</v>
+      </c>
+      <c r="Y90" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z90" s="27" t="s">
         <v>1650</v>
@@ -23960,10 +24281,10 @@
         <v>1650</v>
       </c>
       <c r="S91" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="T91" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="U91" s="27" t="s">
         <v>620</v>
@@ -23972,10 +24293,13 @@
         <v>1654</v>
       </c>
       <c r="W91" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="X91" t="s">
-        <v>2075</v>
+        <v>2076</v>
+      </c>
+      <c r="Y91" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z91" s="27" t="s">
         <v>1650</v>
@@ -24028,22 +24352,25 @@
         <v>1650</v>
       </c>
       <c r="S92" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="T92" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="U92" s="27" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="V92" t="s">
         <v>1654</v>
       </c>
       <c r="W92" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="X92" t="s">
-        <v>2080</v>
+        <v>2081</v>
+      </c>
+      <c r="Y92" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z92" s="27" t="s">
         <v>1650</v>
@@ -24099,22 +24426,25 @@
         <v>1650</v>
       </c>
       <c r="S93" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="T93" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="U93" s="27" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="V93" t="s">
         <v>1654</v>
       </c>
       <c r="W93" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="X93" t="s">
-        <v>2085</v>
+        <v>2086</v>
+      </c>
+      <c r="Y93" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z93" s="27" t="s">
         <v>1650</v>
@@ -24167,30 +24497,33 @@
         <v>1650</v>
       </c>
       <c r="S94" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="T94" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="U94" s="26" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="V94" t="s">
         <v>1654</v>
       </c>
       <c r="W94" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="X94" t="s">
-        <v>2090</v>
-      </c>
-      <c r="Z94" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA94" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB94" s="26" t="s">
+        <v>2091</v>
+      </c>
+      <c r="Y94" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z94" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA94" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB94" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC94">
@@ -24235,22 +24568,25 @@
         <v>1650</v>
       </c>
       <c r="S95" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="T95" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="U95" s="27" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="V95" t="s">
         <v>1654</v>
       </c>
       <c r="W95" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="X95" t="s">
-        <v>2095</v>
+        <v>2096</v>
+      </c>
+      <c r="Y95" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z95" s="27" t="s">
         <v>1650</v>
@@ -24303,30 +24639,33 @@
         <v>1650</v>
       </c>
       <c r="S96" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="T96" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="U96" s="26" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="V96" t="s">
         <v>1654</v>
       </c>
       <c r="W96" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="X96" t="s">
-        <v>2100</v>
-      </c>
-      <c r="Z96" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA96" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB96" s="26" t="s">
+        <v>2101</v>
+      </c>
+      <c r="Y96" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z96" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA96" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB96" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC96">
@@ -24371,22 +24710,22 @@
         <v>1650</v>
       </c>
       <c r="S97" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="T97" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="U97" s="27" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="V97" t="s">
         <v>1654</v>
       </c>
       <c r="W97" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="X97" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="Y97" s="27" t="s">
         <v>1650</v>
@@ -24439,22 +24778,22 @@
         <v>1650</v>
       </c>
       <c r="S98" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="T98" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="U98" s="27" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="V98" t="s">
         <v>1654</v>
       </c>
       <c r="W98" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="X98" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="Y98" s="27" t="s">
         <v>1650</v>
@@ -24513,10 +24852,10 @@
         <v>1650</v>
       </c>
       <c r="S99" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="T99" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="U99" s="27" t="s">
         <v>669</v>
@@ -24525,10 +24864,13 @@
         <v>1654</v>
       </c>
       <c r="W99" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="X99" t="s">
-        <v>2114</v>
+        <v>2115</v>
+      </c>
+      <c r="Y99" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z99" s="27" t="s">
         <v>1650</v>
@@ -24578,10 +24920,10 @@
         <v>1650</v>
       </c>
       <c r="S100" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="T100" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="U100" s="27" t="s">
         <v>675</v>
@@ -24590,10 +24932,10 @@
         <v>1654</v>
       </c>
       <c r="W100" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="X100" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="Y100" s="27" t="s">
         <v>1650</v>
@@ -24649,10 +24991,10 @@
         <v>1650</v>
       </c>
       <c r="S101" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="T101" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="U101" s="27" t="s">
         <v>680</v>
@@ -24661,10 +25003,10 @@
         <v>1654</v>
       </c>
       <c r="W101" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="X101" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="Y101" s="27" t="s">
         <v>1650</v>
@@ -24720,22 +25062,25 @@
         <v>1650</v>
       </c>
       <c r="S102" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="T102" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="U102" s="27" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="V102" t="s">
         <v>1654</v>
       </c>
       <c r="W102" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="X102" t="s">
-        <v>2127</v>
+        <v>2128</v>
+      </c>
+      <c r="Y102" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z102" s="27" t="s">
         <v>1650</v>
@@ -24785,33 +25130,33 @@
         <v>1650</v>
       </c>
       <c r="S103" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="T103" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="U103" s="26" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="V103" t="s">
         <v>1654</v>
       </c>
       <c r="W103" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="X103" t="s">
-        <v>2131</v>
-      </c>
-      <c r="Y103" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z103" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA103" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB103" s="26" t="s">
+        <v>2132</v>
+      </c>
+      <c r="Y103" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z103" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA103" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB103" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC103">
@@ -24859,22 +25204,25 @@
         <v>1650</v>
       </c>
       <c r="S104" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="T104" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="U104" s="27" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="V104" t="s">
         <v>1654</v>
       </c>
       <c r="W104" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="X104" t="s">
-        <v>2136</v>
+        <v>2137</v>
+      </c>
+      <c r="Y104" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z104" s="27" t="s">
         <v>1650</v>
@@ -24927,22 +25275,25 @@
         <v>1650</v>
       </c>
       <c r="S105" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="T105" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="U105" s="27" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="V105" t="s">
         <v>1654</v>
       </c>
       <c r="W105" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="X105" t="s">
-        <v>2141</v>
+        <v>2142</v>
+      </c>
+      <c r="Y105" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z105" s="27" t="s">
         <v>1650</v>
@@ -24995,33 +25346,33 @@
         <v>1650</v>
       </c>
       <c r="S106" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="T106" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="U106" s="26" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="V106" t="s">
         <v>1654</v>
       </c>
       <c r="W106" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="X106" t="s">
-        <v>2146</v>
-      </c>
-      <c r="Y106" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z106" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA106" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB106" s="26" t="s">
+        <v>2147</v>
+      </c>
+      <c r="Y106" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z106" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA106" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB106" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC106">
@@ -25066,22 +25417,25 @@
         <v>1650</v>
       </c>
       <c r="S107" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="T107" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="U107" s="27" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="V107" t="s">
         <v>1654</v>
       </c>
       <c r="W107" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="X107" t="s">
-        <v>2151</v>
+        <v>2152</v>
+      </c>
+      <c r="Y107" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z107" s="27" t="s">
         <v>1650</v>
@@ -25134,22 +25488,25 @@
         <v>1650</v>
       </c>
       <c r="S108" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="T108" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="U108" s="27" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="V108" t="s">
         <v>1654</v>
       </c>
       <c r="W108" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="X108" t="s">
-        <v>2156</v>
+        <v>2157</v>
+      </c>
+      <c r="Y108" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z108" s="27" t="s">
         <v>1650</v>
@@ -25199,25 +25556,34 @@
         <v>1650</v>
       </c>
       <c r="S109" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="T109" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="U109" s="27" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="V109" t="s">
         <v>1654</v>
       </c>
       <c r="W109" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="X109" t="s">
-        <v>2161</v>
+        <v>2162</v>
+      </c>
+      <c r="Y109" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z109" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA109" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB109" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC109">
         <v>37.777479900000003</v>
@@ -25261,22 +25627,25 @@
         <v>1650</v>
       </c>
       <c r="S110" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="T110" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="U110" s="27" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="V110" t="s">
         <v>1654</v>
       </c>
       <c r="W110" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="X110" t="s">
-        <v>2166</v>
+        <v>2167</v>
+      </c>
+      <c r="Y110" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z110" s="27" t="s">
         <v>1650</v>
@@ -25329,10 +25698,10 @@
         <v>1650</v>
       </c>
       <c r="S111" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="T111" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="U111" s="27" t="s">
         <v>739</v>
@@ -25341,10 +25710,13 @@
         <v>1654</v>
       </c>
       <c r="W111" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="X111" t="s">
-        <v>2170</v>
+        <v>2171</v>
+      </c>
+      <c r="Y111" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z111" s="27" t="s">
         <v>1650</v>
@@ -25400,25 +25772,34 @@
         <v>1650</v>
       </c>
       <c r="S112" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="T112" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="U112" s="27" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="V112" t="s">
         <v>1654</v>
       </c>
       <c r="W112" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="X112" t="s">
-        <v>2175</v>
+        <v>2176</v>
+      </c>
+      <c r="Y112" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z112" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA112" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB112" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC112">
         <v>32.283405000000009</v>
@@ -25462,10 +25843,10 @@
         <v>1650</v>
       </c>
       <c r="S113" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="T113" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="U113" s="27" t="s">
         <v>753</v>
@@ -25474,10 +25855,13 @@
         <v>1654</v>
       </c>
       <c r="W113" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="X113" t="s">
-        <v>2179</v>
+        <v>2180</v>
+      </c>
+      <c r="Y113" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z113" s="27" t="s">
         <v>1650</v>
@@ -25527,10 +25911,10 @@
         <v>1650</v>
       </c>
       <c r="S114" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="T114" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="U114" s="27" t="s">
         <v>757</v>
@@ -25539,10 +25923,10 @@
         <v>1654</v>
       </c>
       <c r="W114" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="X114" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="Y114" s="27" t="s">
         <v>1650</v>
@@ -25595,22 +25979,22 @@
         <v>1650</v>
       </c>
       <c r="S115" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="T115" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="U115" s="27" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="V115" t="s">
         <v>1654</v>
       </c>
       <c r="W115" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="X115" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="Y115" s="27" t="s">
         <v>1650</v>
@@ -25663,22 +26047,22 @@
         <v>1650</v>
       </c>
       <c r="S116" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="T116" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="U116" s="27" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="V116" t="s">
         <v>1654</v>
       </c>
       <c r="W116" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="X116" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="Y116" s="27" t="s">
         <v>1650</v>
@@ -25728,13 +26112,13 @@
         <v>776</v>
       </c>
       <c r="N117" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="P117" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="S117" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="118" spans="1:30">
@@ -25772,22 +26156,25 @@
         <v>1650</v>
       </c>
       <c r="S118" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="T118" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="U118" s="27" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="V118" t="s">
         <v>1654</v>
       </c>
       <c r="W118" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="X118" t="s">
-        <v>2199</v>
+        <v>2200</v>
+      </c>
+      <c r="Y118" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z118" s="27" t="s">
         <v>1650</v>
@@ -25840,10 +26227,10 @@
         <v>1650</v>
       </c>
       <c r="S119" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="T119" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="U119" s="27" t="s">
         <v>783</v>
@@ -25852,10 +26239,10 @@
         <v>1654</v>
       </c>
       <c r="W119" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="X119" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="Y119" s="27" t="s">
         <v>1650</v>
@@ -25908,22 +26295,22 @@
         <v>1650</v>
       </c>
       <c r="S120" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="T120" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="U120" s="27" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="V120" t="s">
         <v>1654</v>
       </c>
       <c r="W120" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="X120" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="Y120" s="27" t="s">
         <v>1650</v>
@@ -25979,28 +26366,34 @@
         <v>1650</v>
       </c>
       <c r="S121" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="T121" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="U121" s="26" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="V121" t="s">
         <v>1654</v>
       </c>
       <c r="W121" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="X121" t="s">
-        <v>2213</v>
-      </c>
-      <c r="Z121" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA121" s="26" t="s">
-        <v>1650</v>
+        <v>2214</v>
+      </c>
+      <c r="Y121" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z121" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA121" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB121" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC121">
         <v>47.679950100000013</v>
@@ -26044,10 +26437,10 @@
         <v>1650</v>
       </c>
       <c r="S122" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="T122" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="U122" s="27" t="s">
         <v>799</v>
@@ -26056,10 +26449,13 @@
         <v>1654</v>
       </c>
       <c r="W122" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="X122" t="s">
-        <v>2217</v>
+        <v>2218</v>
+      </c>
+      <c r="Y122" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z122" s="27" t="s">
         <v>1650</v>
@@ -26112,10 +26508,10 @@
         <v>1650</v>
       </c>
       <c r="S123" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="T123" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="U123" s="27" t="s">
         <v>805</v>
@@ -26124,10 +26520,13 @@
         <v>1654</v>
       </c>
       <c r="W123" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="X123" t="s">
-        <v>2221</v>
+        <v>2222</v>
+      </c>
+      <c r="Y123" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z123" s="27" t="s">
         <v>1650</v>
@@ -26206,22 +26605,22 @@
         <v>1650</v>
       </c>
       <c r="S125" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="T125" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="U125" s="27" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="V125" t="s">
         <v>1654</v>
       </c>
       <c r="W125" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="X125" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="Y125" s="27" t="s">
         <v>1650</v>
@@ -26274,10 +26673,10 @@
         <v>1650</v>
       </c>
       <c r="S126" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="T126" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="U126" s="27" t="s">
         <v>821</v>
@@ -26286,10 +26685,10 @@
         <v>1654</v>
       </c>
       <c r="W126" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="X126" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="Y126" s="27" t="s">
         <v>1650</v>
@@ -26345,22 +26744,22 @@
         <v>1650</v>
       </c>
       <c r="S127" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="T127" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="U127" s="27" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="V127" t="s">
         <v>1654</v>
       </c>
       <c r="W127" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="X127" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="Y127" s="27" t="s">
         <v>1650</v>
@@ -26410,13 +26809,13 @@
         <v>839</v>
       </c>
       <c r="N128" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="P128" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="S128" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="129" spans="1:30">
@@ -26454,25 +26853,31 @@
         <v>1650</v>
       </c>
       <c r="S129" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="T129" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="U129" s="27" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="V129" t="s">
         <v>1654</v>
       </c>
       <c r="W129" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="X129" t="s">
-        <v>2241</v>
+        <v>2242</v>
+      </c>
+      <c r="Y129" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z129" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AA129" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AB129" s="27" t="s">
         <v>1650</v>
@@ -26519,10 +26924,10 @@
         <v>1650</v>
       </c>
       <c r="S130" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="T130" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="U130" s="27" t="s">
         <v>847</v>
@@ -26531,10 +26936,19 @@
         <v>1654</v>
       </c>
       <c r="W130" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="X130" t="s">
-        <v>2245</v>
+        <v>2246</v>
+      </c>
+      <c r="Y130" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z130" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA130" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AB130" s="27" t="s">
         <v>1650</v>
@@ -26581,10 +26995,10 @@
         <v>1650</v>
       </c>
       <c r="S131" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="T131" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="U131" s="27" t="s">
         <v>852</v>
@@ -26593,10 +27007,13 @@
         <v>1654</v>
       </c>
       <c r="W131" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="X131" t="s">
-        <v>2249</v>
+        <v>2250</v>
+      </c>
+      <c r="Y131" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z131" s="27" t="s">
         <v>1650</v>
@@ -26649,10 +27066,10 @@
         <v>1650</v>
       </c>
       <c r="S132" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="T132" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="U132" s="27" t="s">
         <v>857</v>
@@ -26661,10 +27078,10 @@
         <v>1654</v>
       </c>
       <c r="W132" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="X132" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="Y132" s="27" t="s">
         <v>1650</v>
@@ -26746,10 +27163,10 @@
         <v>1650</v>
       </c>
       <c r="S134" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="T134" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="U134" s="27" t="s">
         <v>869</v>
@@ -26758,10 +27175,13 @@
         <v>1654</v>
       </c>
       <c r="W134" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="X134" t="s">
-        <v>2257</v>
+        <v>2258</v>
+      </c>
+      <c r="Y134" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z134" s="27" t="s">
         <v>1650</v>
@@ -26817,25 +27237,34 @@
         <v>1650</v>
       </c>
       <c r="S135" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="T135" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="U135" s="26" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="V135" t="s">
         <v>1654</v>
       </c>
       <c r="W135" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="X135" t="s">
-        <v>2262</v>
-      </c>
-      <c r="AA135" s="26" t="s">
-        <v>1650</v>
+        <v>2263</v>
+      </c>
+      <c r="Y135" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z135" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA135" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB135" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC135">
         <v>36.130641199999999</v>
@@ -26882,22 +27311,25 @@
         <v>1650</v>
       </c>
       <c r="S136" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="T136" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="U136" s="27" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="V136" t="s">
         <v>1654</v>
       </c>
       <c r="W136" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="X136" t="s">
-        <v>2267</v>
+        <v>2268</v>
+      </c>
+      <c r="Y136" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z136" s="27" t="s">
         <v>1650</v>
@@ -26947,22 +27379,25 @@
         <v>1650</v>
       </c>
       <c r="S137" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="T137" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="U137" s="27" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="V137" t="s">
         <v>1654</v>
       </c>
       <c r="W137" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="X137" t="s">
-        <v>2272</v>
+        <v>2273</v>
+      </c>
+      <c r="Y137" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z137" s="27" t="s">
         <v>1650</v>
@@ -27015,22 +27450,22 @@
         <v>1650</v>
       </c>
       <c r="S138" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="T138" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="U138" s="27" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="V138" t="s">
         <v>1654</v>
       </c>
       <c r="W138" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="X138" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="Y138" s="27" t="s">
         <v>1650</v>
@@ -27086,22 +27521,22 @@
         <v>1650</v>
       </c>
       <c r="S139" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="T139" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="U139" s="27" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="V139" t="s">
         <v>1654</v>
       </c>
       <c r="W139" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="X139" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="Y139" s="27" t="s">
         <v>1650</v>
@@ -27157,22 +27592,25 @@
         <v>1650</v>
       </c>
       <c r="S140" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="T140" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="U140" s="27" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="V140" t="s">
         <v>1654</v>
       </c>
       <c r="W140" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="X140" t="s">
-        <v>2287</v>
+        <v>2288</v>
+      </c>
+      <c r="Y140" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z140" s="27" t="s">
         <v>1650</v>
@@ -27216,13 +27654,13 @@
         <v>916</v>
       </c>
       <c r="N141" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="P141" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="S141" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="142" spans="1:30">
@@ -27257,10 +27695,10 @@
         <v>1650</v>
       </c>
       <c r="S142" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="T142" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="U142" s="27" t="s">
         <v>917</v>
@@ -27269,10 +27707,10 @@
         <v>1654</v>
       </c>
       <c r="W142" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="X142" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="Y142" s="27" t="s">
         <v>1650</v>
@@ -27328,10 +27766,10 @@
         <v>1650</v>
       </c>
       <c r="S143" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="T143" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="U143" s="27" t="s">
         <v>917</v>
@@ -27340,10 +27778,10 @@
         <v>1654</v>
       </c>
       <c r="W143" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="X143" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="Y143" s="27" t="s">
         <v>1650</v>
@@ -27399,10 +27837,10 @@
         <v>1650</v>
       </c>
       <c r="S144" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="T144" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="U144" s="27" t="s">
         <v>917</v>
@@ -27411,10 +27849,10 @@
         <v>1654</v>
       </c>
       <c r="W144" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="X144" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="Y144" s="27" t="s">
         <v>1650</v>
@@ -27470,22 +27908,22 @@
         <v>1650</v>
       </c>
       <c r="S145" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="T145" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="U145" s="27" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="V145" t="s">
         <v>1654</v>
       </c>
       <c r="W145" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="X145" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="Y145" s="27" t="s">
         <v>1650</v>
@@ -27544,22 +27982,25 @@
         <v>1650</v>
       </c>
       <c r="S146" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="T146" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="U146" s="27" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="V146" t="s">
         <v>1654</v>
       </c>
       <c r="W146" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="X146" t="s">
-        <v>2310</v>
+        <v>2311</v>
+      </c>
+      <c r="Y146" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z146" s="27" t="s">
         <v>1650</v>
@@ -27612,22 +28053,25 @@
         <v>1650</v>
       </c>
       <c r="S147" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="T147" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="U147" s="27" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="V147" t="s">
         <v>1654</v>
       </c>
       <c r="W147" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="X147" t="s">
-        <v>2315</v>
+        <v>2316</v>
+      </c>
+      <c r="Y147" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z147" s="27" t="s">
         <v>1650</v>
@@ -27680,22 +28124,22 @@
         <v>1650</v>
       </c>
       <c r="S148" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="T148" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="U148" s="27" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="V148" t="s">
         <v>1654</v>
       </c>
       <c r="W148" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="X148" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="Y148" s="27" t="s">
         <v>1650</v>
@@ -27751,22 +28195,25 @@
         <v>1650</v>
       </c>
       <c r="S149" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="T149" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="U149" s="27" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="V149" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="W149" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="X149" t="s">
-        <v>2326</v>
+        <v>2327</v>
+      </c>
+      <c r="Y149" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z149" s="27" t="s">
         <v>1650</v>
@@ -27819,22 +28266,34 @@
         <v>1650</v>
       </c>
       <c r="S150" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="T150" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="U150" s="26" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="V150" t="s">
         <v>1654</v>
       </c>
       <c r="W150" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="X150" t="s">
-        <v>2331</v>
+        <v>2332</v>
+      </c>
+      <c r="Y150" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z150" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA150" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB150" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC150">
         <v>41.308016000000002</v>
@@ -27878,22 +28337,22 @@
         <v>1650</v>
       </c>
       <c r="S151" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="T151" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="U151" s="27" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="V151" t="s">
         <v>1654</v>
       </c>
       <c r="W151" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="X151" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="Y151" s="27" t="s">
         <v>1650</v>
@@ -27949,33 +28408,33 @@
         <v>1650</v>
       </c>
       <c r="S152" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="T152" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="U152" s="26" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="V152" t="s">
         <v>1654</v>
       </c>
       <c r="W152" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="X152" t="s">
-        <v>2341</v>
-      </c>
-      <c r="Y152" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z152" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA152" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB152" s="26" t="s">
+        <v>2342</v>
+      </c>
+      <c r="Y152" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z152" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA152" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB152" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC152">
@@ -28020,25 +28479,34 @@
         <v>1650</v>
       </c>
       <c r="S153" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="T153" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="U153" s="27" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="V153" t="s">
         <v>1654</v>
       </c>
       <c r="W153" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="X153" t="s">
-        <v>2346</v>
+        <v>2347</v>
+      </c>
+      <c r="Y153" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z153" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA153" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB153" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC153">
         <v>38.56458469999999</v>
@@ -28082,25 +28550,34 @@
         <v>1650</v>
       </c>
       <c r="S154" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="T154" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="U154" s="26" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="V154" t="s">
         <v>1654</v>
       </c>
       <c r="W154" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="X154" t="s">
-        <v>2351</v>
-      </c>
-      <c r="AA154" s="26" t="s">
-        <v>1650</v>
+        <v>2352</v>
+      </c>
+      <c r="Y154" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z154" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA154" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB154" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC154">
         <v>33.665809000000003</v>
@@ -28144,22 +28621,22 @@
         <v>1650</v>
       </c>
       <c r="S155" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="T155" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="U155" s="27" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="V155" t="s">
         <v>1654</v>
       </c>
       <c r="W155" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="X155" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="Y155" s="27" t="s">
         <v>1650</v>
@@ -28215,22 +28692,22 @@
         <v>1650</v>
       </c>
       <c r="S156" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="T156" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="U156" s="27" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="V156" t="s">
         <v>1654</v>
       </c>
       <c r="W156" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="X156" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="Y156" s="27" t="s">
         <v>1650</v>
@@ -28286,30 +28763,33 @@
         <v>1650</v>
       </c>
       <c r="S157" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="T157" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="U157" s="26" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="V157" t="s">
         <v>1654</v>
       </c>
       <c r="W157" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="X157" t="s">
-        <v>2366</v>
-      </c>
-      <c r="Z157" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA157" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB157" s="26" t="s">
+        <v>2367</v>
+      </c>
+      <c r="Y157" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z157" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA157" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB157" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC157">
@@ -28351,22 +28831,25 @@
         <v>1650</v>
       </c>
       <c r="S158" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="T158" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="U158" s="27" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="V158" t="s">
         <v>1654</v>
       </c>
       <c r="W158" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="X158" t="s">
-        <v>2371</v>
+        <v>2372</v>
+      </c>
+      <c r="Y158" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z158" s="27" t="s">
         <v>1650</v>
@@ -28419,10 +28902,10 @@
         <v>1650</v>
       </c>
       <c r="S159" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="T159" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="U159" s="27" t="s">
         <v>1023</v>
@@ -28431,10 +28914,10 @@
         <v>1654</v>
       </c>
       <c r="W159" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="X159" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="Y159" s="27" t="s">
         <v>1650</v>
@@ -28490,22 +28973,25 @@
         <v>1650</v>
       </c>
       <c r="S160" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="T160" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="U160" s="27" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="V160" t="s">
         <v>1654</v>
       </c>
       <c r="W160" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="X160" t="s">
-        <v>2380</v>
+        <v>2381</v>
+      </c>
+      <c r="Y160" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z160" s="27" t="s">
         <v>1650</v>
@@ -28558,28 +29044,34 @@
         <v>1650</v>
       </c>
       <c r="S161" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="T161" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="U161" s="27" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="V161" t="s">
         <v>1654</v>
       </c>
       <c r="W161" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="X161" t="s">
-        <v>2385</v>
+        <v>2386</v>
+      </c>
+      <c r="Y161" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z161" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA161" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB161" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC161">
         <v>31.9227949</v>
@@ -28623,22 +29115,25 @@
         <v>1650</v>
       </c>
       <c r="S162" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="T162" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="U162" s="27" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="V162" t="s">
         <v>1654</v>
       </c>
       <c r="W162" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="X162" t="s">
-        <v>2390</v>
+        <v>2391</v>
+      </c>
+      <c r="Y162" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z162" s="27" t="s">
         <v>1650</v>
@@ -28691,33 +29186,33 @@
         <v>1650</v>
       </c>
       <c r="S163" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="T163" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="U163" s="26" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="V163" t="s">
         <v>1654</v>
       </c>
       <c r="W163" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="X163" t="s">
-        <v>2395</v>
-      </c>
-      <c r="Y163" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z163" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA163" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB163" s="26" t="s">
+        <v>2396</v>
+      </c>
+      <c r="Y163" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z163" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA163" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB163" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC163">
@@ -28762,10 +29257,10 @@
         <v>1650</v>
       </c>
       <c r="S164" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="T164" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="U164" s="27" t="s">
         <v>1054</v>
@@ -28774,10 +29269,13 @@
         <v>1654</v>
       </c>
       <c r="W164" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="X164" t="s">
-        <v>2399</v>
+        <v>2400</v>
+      </c>
+      <c r="Y164" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z164" s="27" t="s">
         <v>1650</v>
@@ -28830,22 +29328,22 @@
         <v>1650</v>
       </c>
       <c r="S165" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="T165" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="U165" s="27" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="V165" t="s">
         <v>1654</v>
       </c>
       <c r="W165" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="X165" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="Y165" s="27" t="s">
         <v>1650</v>
@@ -28901,10 +29399,10 @@
         <v>1650</v>
       </c>
       <c r="S166" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="T166" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="U166" s="27" t="s">
         <v>1065</v>
@@ -28913,10 +29411,10 @@
         <v>1654</v>
       </c>
       <c r="W166" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="X166" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="Y166" s="27" t="s">
         <v>1650</v>
@@ -28972,10 +29470,10 @@
         <v>1650</v>
       </c>
       <c r="S167" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="T167" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="U167" s="27" t="s">
         <v>1070</v>
@@ -28984,10 +29482,13 @@
         <v>1654</v>
       </c>
       <c r="W167" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="X167" t="s">
-        <v>2412</v>
+        <v>2413</v>
+      </c>
+      <c r="Y167" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z167" s="27" t="s">
         <v>1650</v>
@@ -29040,22 +29541,22 @@
         <v>1650</v>
       </c>
       <c r="S168" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="T168" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="U168" s="27" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="V168" t="s">
         <v>1654</v>
       </c>
       <c r="W168" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="X168" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="Y168" s="27" t="s">
         <v>1650</v>
@@ -29111,22 +29612,25 @@
         <v>1650</v>
       </c>
       <c r="S169" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="T169" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="U169" s="27" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="V169" t="s">
         <v>1654</v>
       </c>
       <c r="W169" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="X169" t="s">
-        <v>2422</v>
+        <v>2423</v>
+      </c>
+      <c r="Y169" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z169" s="27" t="s">
         <v>1650</v>
@@ -29179,33 +29683,33 @@
         <v>1650</v>
       </c>
       <c r="S170" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="T170" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="U170" s="26" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="V170" t="s">
         <v>1654</v>
       </c>
       <c r="W170" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="X170" t="s">
-        <v>2427</v>
-      </c>
-      <c r="Y170" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z170" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA170" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB170" s="26" t="s">
+        <v>2428</v>
+      </c>
+      <c r="Y170" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z170" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA170" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB170" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC170">
@@ -29250,10 +29754,10 @@
         <v>1650</v>
       </c>
       <c r="S171" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="T171" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="U171" s="27" t="s">
         <v>1094</v>
@@ -29262,10 +29766,13 @@
         <v>1654</v>
       </c>
       <c r="W171" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="X171" t="s">
-        <v>2431</v>
+        <v>2432</v>
+      </c>
+      <c r="Y171" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z171" s="27" t="s">
         <v>1650</v>
@@ -29315,22 +29822,34 @@
         <v>1650</v>
       </c>
       <c r="S172" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="T172" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="U172" s="27" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="V172" t="s">
         <v>1654</v>
       </c>
       <c r="W172" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="X172" t="s">
-        <v>2436</v>
+        <v>2437</v>
+      </c>
+      <c r="Y172" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z172" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA172" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB172" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC172">
         <v>40.737025000000003</v>
@@ -29374,25 +29893,34 @@
         <v>1650</v>
       </c>
       <c r="S173" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="T173" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="U173" s="27" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="V173" t="s">
         <v>1654</v>
       </c>
       <c r="W173" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="X173" t="s">
-        <v>2441</v>
+        <v>2442</v>
+      </c>
+      <c r="Y173" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z173" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA173" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB173" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC173">
         <v>38.032451000000009</v>
@@ -29436,22 +29964,22 @@
         <v>1650</v>
       </c>
       <c r="S174" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="T174" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="U174" s="27" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="V174" t="s">
         <v>1654</v>
       </c>
       <c r="W174" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="X174" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="Y174" s="27" t="s">
         <v>1650</v>
@@ -29536,28 +30064,34 @@
         <v>1650</v>
       </c>
       <c r="S176" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="T176" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="U176" s="27" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V176" t="s">
         <v>1654</v>
       </c>
       <c r="W176" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="X176" t="s">
-        <v>2451</v>
+        <v>2452</v>
+      </c>
+      <c r="Y176" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z176" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA176" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB176" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC176">
         <v>29.643404000000011</v>
@@ -29601,22 +30135,22 @@
         <v>1650</v>
       </c>
       <c r="S177" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="T177" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="U177" s="27" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="V177" t="s">
         <v>1654</v>
       </c>
       <c r="W177" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="X177" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="Y177" s="27" t="s">
         <v>1650</v>
@@ -29675,10 +30209,10 @@
         <v>1650</v>
       </c>
       <c r="S178" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="T178" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="U178" s="26" t="s">
         <v>1134</v>
@@ -29687,18 +30221,21 @@
         <v>1654</v>
       </c>
       <c r="W178" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="X178" t="s">
-        <v>2460</v>
-      </c>
-      <c r="Z178" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA178" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB178" s="26" t="s">
+        <v>2461</v>
+      </c>
+      <c r="Y178" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z178" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA178" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB178" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC178">
@@ -29740,25 +30277,34 @@
         <v>1650</v>
       </c>
       <c r="S179" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="T179" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="U179" s="27" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="V179" t="s">
         <v>1654</v>
       </c>
       <c r="W179" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="X179" t="s">
-        <v>2465</v>
+        <v>2466</v>
+      </c>
+      <c r="Y179" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z179" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA179" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB179" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC179">
         <v>35.237008500000002</v>
@@ -29825,28 +30371,34 @@
         <v>1650</v>
       </c>
       <c r="S181" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="T181" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="U181" s="27" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="V181" t="s">
         <v>1654</v>
       </c>
       <c r="W181" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="X181" t="s">
-        <v>2470</v>
+        <v>2471</v>
+      </c>
+      <c r="Y181" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z181" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA181" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB181" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC181">
         <v>35.104783900000001</v>
@@ -29893,22 +30445,22 @@
         <v>1650</v>
       </c>
       <c r="S182" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="T182" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="U182" s="27" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="V182" t="s">
         <v>1654</v>
       </c>
       <c r="W182" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="X182" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="Y182" s="27" t="s">
         <v>1650</v>
@@ -29964,10 +30516,10 @@
         <v>1650</v>
       </c>
       <c r="S183" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="T183" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="U183" s="27" t="s">
         <v>1162</v>
@@ -29976,10 +30528,13 @@
         <v>1654</v>
       </c>
       <c r="W183" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="X183" t="s">
-        <v>2479</v>
+        <v>2480</v>
+      </c>
+      <c r="Y183" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z183" s="27" t="s">
         <v>1650</v>
@@ -30029,22 +30584,22 @@
         <v>1650</v>
       </c>
       <c r="S184" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="T184" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="U184" s="27" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="V184" t="s">
         <v>1654</v>
       </c>
       <c r="W184" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="X184" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="Y184" s="27" t="s">
         <v>1650</v>
@@ -30100,22 +30655,25 @@
         <v>1650</v>
       </c>
       <c r="S185" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="T185" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="U185" s="27" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="V185" t="s">
         <v>1654</v>
       </c>
       <c r="W185" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="X185" t="s">
-        <v>2489</v>
+        <v>2490</v>
+      </c>
+      <c r="Y185" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z185" s="27" t="s">
         <v>1650</v>
@@ -30165,22 +30723,25 @@
         <v>1650</v>
       </c>
       <c r="S186" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="T186" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="U186" s="27" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="V186" t="s">
         <v>1654</v>
       </c>
       <c r="W186" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="X186" t="s">
-        <v>2494</v>
+        <v>2495</v>
+      </c>
+      <c r="Y186" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z186" s="27" t="s">
         <v>1650</v>
@@ -30233,22 +30794,34 @@
         <v>1650</v>
       </c>
       <c r="S187" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="T187" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="U187" s="26" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="V187" t="s">
         <v>1654</v>
       </c>
       <c r="W187" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="X187" t="s">
-        <v>2499</v>
+        <v>2500</v>
+      </c>
+      <c r="Y187" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z187" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA187" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB187" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC187">
         <v>40.843272800000008</v>
@@ -30292,25 +30865,34 @@
         <v>1650</v>
       </c>
       <c r="S188" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="T188" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="U188" s="27" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="V188" t="s">
         <v>1654</v>
       </c>
       <c r="W188" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="X188" t="s">
-        <v>2504</v>
+        <v>2505</v>
+      </c>
+      <c r="Y188" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z188" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA188" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB188" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC188">
         <v>40.972490400000012</v>
@@ -30354,22 +30936,22 @@
         <v>1650</v>
       </c>
       <c r="S189" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="T189" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="U189" s="27" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="V189" t="s">
         <v>1654</v>
       </c>
       <c r="W189" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="X189" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="Y189" s="27" t="s">
         <v>1650</v>
@@ -30425,28 +31007,34 @@
         <v>1650</v>
       </c>
       <c r="S190" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="T190" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="U190" s="27" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="V190" t="s">
         <v>1654</v>
       </c>
       <c r="W190" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="X190" t="s">
-        <v>2514</v>
+        <v>2515</v>
+      </c>
+      <c r="Y190" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z190" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA190" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB190" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC190">
         <v>30.836199999999991</v>
@@ -30490,22 +31078,34 @@
         <v>1650</v>
       </c>
       <c r="S191" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="T191" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="U191" s="27" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="V191" t="s">
         <v>1654</v>
       </c>
       <c r="W191" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="X191" t="s">
-        <v>2519</v>
+        <v>2520</v>
+      </c>
+      <c r="Y191" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z191" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA191" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB191" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC191">
         <v>36.4830142</v>
@@ -30549,22 +31149,25 @@
         <v>1650</v>
       </c>
       <c r="S192" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="T192" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="U192" s="27" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V192" t="s">
         <v>1654</v>
       </c>
       <c r="W192" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="X192" t="s">
-        <v>2524</v>
+        <v>2525</v>
+      </c>
+      <c r="Y192" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z192" s="27" t="s">
         <v>1650</v>
@@ -30617,22 +31220,25 @@
         <v>1650</v>
       </c>
       <c r="S193" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="T193" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="U193" s="27" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="V193" t="s">
         <v>1654</v>
       </c>
       <c r="W193" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="X193" t="s">
-        <v>2529</v>
+        <v>2530</v>
+      </c>
+      <c r="Y193" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z193" s="27" t="s">
         <v>1650</v>
@@ -30685,22 +31291,25 @@
         <v>1650</v>
       </c>
       <c r="S194" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="T194" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="U194" s="27" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="V194" t="s">
         <v>1654</v>
       </c>
       <c r="W194" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="X194" t="s">
-        <v>2534</v>
+        <v>2535</v>
+      </c>
+      <c r="Y194" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z194" s="27" t="s">
         <v>1650</v>
@@ -30753,25 +31362,31 @@
         <v>1650</v>
       </c>
       <c r="S195" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="T195" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="U195" s="27" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="V195" t="s">
         <v>1654</v>
       </c>
       <c r="W195" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="X195" t="s">
-        <v>2539</v>
+        <v>2540</v>
+      </c>
+      <c r="Y195" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z195" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AA195" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AB195" s="27" t="s">
         <v>1650</v>
@@ -30821,33 +31436,33 @@
         <v>1650</v>
       </c>
       <c r="S196" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="T196" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="U196" s="26" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="V196" t="s">
         <v>1654</v>
       </c>
       <c r="W196" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="X196" t="s">
-        <v>2544</v>
-      </c>
-      <c r="Y196" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z196" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA196" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB196" s="26" t="s">
+        <v>2545</v>
+      </c>
+      <c r="Y196" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z196" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA196" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB196" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC196">
@@ -30892,10 +31507,10 @@
         <v>1650</v>
       </c>
       <c r="S197" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="T197" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="U197" s="27" t="s">
         <v>1247</v>
@@ -30904,10 +31519,13 @@
         <v>1654</v>
       </c>
       <c r="W197" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="X197" t="s">
-        <v>2548</v>
+        <v>2549</v>
+      </c>
+      <c r="Y197" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z197" s="27" t="s">
         <v>1650</v>
@@ -30960,22 +31578,22 @@
         <v>1650</v>
       </c>
       <c r="S198" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="T198" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="U198" s="27" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="V198" t="s">
         <v>1654</v>
       </c>
       <c r="W198" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="X198" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="Y198" s="27" t="s">
         <v>1650</v>
@@ -31031,22 +31649,25 @@
         <v>1650</v>
       </c>
       <c r="S199" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="T199" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="U199" s="27" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="V199" t="s">
         <v>1654</v>
       </c>
       <c r="W199" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="X199" t="s">
-        <v>2558</v>
+        <v>2559</v>
+      </c>
+      <c r="Y199" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z199" s="27" t="s">
         <v>1650</v>
@@ -31099,22 +31720,22 @@
         <v>1650</v>
       </c>
       <c r="S200" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="T200" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="U200" s="27" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="V200" t="s">
         <v>1654</v>
       </c>
       <c r="W200" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="X200" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="Y200" s="27" t="s">
         <v>1650</v>
@@ -31170,22 +31791,25 @@
         <v>1650</v>
       </c>
       <c r="S201" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="T201" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="U201" s="27" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="V201" t="s">
         <v>1654</v>
       </c>
       <c r="W201" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="X201" t="s">
-        <v>2568</v>
+        <v>2569</v>
+      </c>
+      <c r="Y201" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z201" s="27" t="s">
         <v>1650</v>
@@ -31238,10 +31862,10 @@
         <v>1650</v>
       </c>
       <c r="S202" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="T202" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="U202" s="27" t="s">
         <v>1281</v>
@@ -31250,10 +31874,10 @@
         <v>1654</v>
       </c>
       <c r="W202" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="X202" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="Y202" s="27" t="s">
         <v>1650</v>
@@ -31312,22 +31936,25 @@
         <v>1650</v>
       </c>
       <c r="S203" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="T203" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="U203" s="27" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="V203" t="s">
         <v>1654</v>
       </c>
       <c r="W203" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="X203" t="s">
-        <v>2577</v>
+        <v>2578</v>
+      </c>
+      <c r="Y203" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z203" s="27" t="s">
         <v>1650</v>
@@ -31380,22 +32007,25 @@
         <v>1650</v>
       </c>
       <c r="S204" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="T204" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="U204" s="27" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="V204" t="s">
         <v>1654</v>
       </c>
       <c r="W204" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="X204" t="s">
-        <v>2582</v>
+        <v>2583</v>
+      </c>
+      <c r="Y204" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z204" s="27" t="s">
         <v>1650</v>
@@ -31448,22 +32078,25 @@
         <v>1650</v>
       </c>
       <c r="S205" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="T205" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="U205" s="27" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="V205" t="s">
         <v>1654</v>
       </c>
       <c r="W205" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="X205" t="s">
-        <v>2587</v>
+        <v>2588</v>
+      </c>
+      <c r="Y205" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z205" s="27" t="s">
         <v>1650</v>
@@ -31516,22 +32149,34 @@
         <v>1650</v>
       </c>
       <c r="S206" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="T206" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="U206" s="27" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="V206" t="s">
         <v>1654</v>
       </c>
       <c r="W206" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="X206" t="s">
-        <v>2592</v>
+        <v>2593</v>
+      </c>
+      <c r="Y206" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z206" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA206" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB206" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC206">
         <v>37.790966399999988</v>
@@ -31572,22 +32217,25 @@
         <v>1650</v>
       </c>
       <c r="S207" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="T207" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="U207" s="27" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="V207" t="s">
         <v>1654</v>
       </c>
       <c r="W207" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="X207" t="s">
-        <v>2597</v>
+        <v>2598</v>
+      </c>
+      <c r="Y207" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z207" s="27" t="s">
         <v>1650</v>
@@ -31637,22 +32285,22 @@
         <v>1650</v>
       </c>
       <c r="S208" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="T208" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="U208" s="27" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="V208" t="s">
         <v>1654</v>
       </c>
       <c r="W208" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="X208" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="Y208" s="27" t="s">
         <v>1650</v>
@@ -31708,22 +32356,22 @@
         <v>1650</v>
       </c>
       <c r="S209" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="T209" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="U209" s="27" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="V209" t="s">
         <v>1654</v>
       </c>
       <c r="W209" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="X209" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="Y209" s="27" t="s">
         <v>1650</v>
@@ -31779,22 +32427,22 @@
         <v>1650</v>
       </c>
       <c r="S210" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="T210" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="U210" s="27" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="V210" t="s">
         <v>1654</v>
       </c>
       <c r="W210" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="X210" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="Y210" s="27" t="s">
         <v>1650</v>
@@ -31850,22 +32498,25 @@
         <v>1650</v>
       </c>
       <c r="S211" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="T211" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="U211" s="27" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="V211" t="s">
         <v>1654</v>
       </c>
       <c r="W211" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="X211" t="s">
-        <v>2617</v>
+        <v>2618</v>
+      </c>
+      <c r="Y211" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z211" s="27" t="s">
         <v>1650</v>
@@ -31918,25 +32569,34 @@
         <v>1650</v>
       </c>
       <c r="S212" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="T212" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="U212" s="27" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="V212" t="s">
         <v>1654</v>
       </c>
       <c r="W212" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="X212" t="s">
-        <v>2622</v>
+        <v>2623</v>
+      </c>
+      <c r="Y212" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z212" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA212" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB212" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC212">
         <v>35.881701999999997</v>
@@ -31980,22 +32640,25 @@
         <v>1650</v>
       </c>
       <c r="S213" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="T213" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="U213" s="27" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="V213" t="s">
         <v>1654</v>
       </c>
       <c r="W213" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="X213" t="s">
-        <v>2627</v>
+        <v>2628</v>
+      </c>
+      <c r="Y213" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z213" s="27" t="s">
         <v>1650</v>
@@ -32051,10 +32714,10 @@
         <v>1650</v>
       </c>
       <c r="S214" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="T214" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="U214" s="27" t="s">
         <v>1353</v>
@@ -32063,10 +32726,13 @@
         <v>1654</v>
       </c>
       <c r="W214" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="X214" t="s">
-        <v>2631</v>
+        <v>2632</v>
+      </c>
+      <c r="Y214" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z214" s="27" t="s">
         <v>1650</v>
@@ -32119,22 +32785,25 @@
         <v>1650</v>
       </c>
       <c r="S215" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="T215" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="U215" s="27" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="V215" t="s">
         <v>1654</v>
       </c>
       <c r="W215" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="X215" t="s">
-        <v>2636</v>
+        <v>2637</v>
+      </c>
+      <c r="Y215" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z215" s="27" t="s">
         <v>1650</v>
@@ -32187,22 +32856,22 @@
         <v>1650</v>
       </c>
       <c r="S216" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="T216" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="U216" s="27" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="V216" t="s">
         <v>1654</v>
       </c>
       <c r="W216" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="X216" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="Y216" s="27" t="s">
         <v>1650</v>
@@ -32258,22 +32927,25 @@
         <v>1650</v>
       </c>
       <c r="S217" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="T217" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="U217" s="27" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="V217" t="s">
         <v>1654</v>
       </c>
       <c r="W217" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="X217" t="s">
-        <v>2646</v>
+        <v>2647</v>
+      </c>
+      <c r="Y217" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z217" s="27" t="s">
         <v>1650</v>
@@ -32326,22 +32998,25 @@
         <v>1650</v>
       </c>
       <c r="S218" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="T218" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="U218" s="27" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="V218" t="s">
         <v>1654</v>
       </c>
       <c r="W218" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="X218" t="s">
-        <v>2651</v>
+        <v>2652</v>
+      </c>
+      <c r="Y218" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z218" s="27" t="s">
         <v>1650</v>
@@ -32394,22 +33069,28 @@
         <v>1650</v>
       </c>
       <c r="S219" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="T219" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="U219" s="27" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="V219" t="s">
         <v>1654</v>
       </c>
       <c r="W219" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="X219" t="s">
-        <v>2656</v>
+        <v>2657</v>
+      </c>
+      <c r="Y219" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z219" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA219" s="27" t="s">
         <v>1650</v>
@@ -32462,25 +33143,34 @@
         <v>1650</v>
       </c>
       <c r="S220" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="T220" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="U220" s="27" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="V220" t="s">
         <v>1654</v>
       </c>
       <c r="W220" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="X220" t="s">
-        <v>2661</v>
+        <v>2662</v>
+      </c>
+      <c r="Y220" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z220" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA220" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB220" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC220">
         <v>18.335094000000002</v>
@@ -32567,13 +33257,13 @@
         <v>1412</v>
       </c>
       <c r="N223" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="P223" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="S223" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="224" spans="1:30">
@@ -32611,10 +33301,10 @@
         <v>1650</v>
       </c>
       <c r="S224" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="T224" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="U224" s="27" t="s">
         <v>1413</v>
@@ -32623,10 +33313,10 @@
         <v>1654</v>
       </c>
       <c r="W224" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="X224" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="Y224" s="27" t="s">
         <v>1650</v>
@@ -32676,22 +33366,34 @@
         <v>1650</v>
       </c>
       <c r="S225" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="T225" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="U225" s="27" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="V225" t="s">
         <v>1654</v>
       </c>
       <c r="W225" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="X225" t="s">
-        <v>2671</v>
+        <v>2672</v>
+      </c>
+      <c r="Y225" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z225" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA225" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB225" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC225">
         <v>12.498204599999999</v>
@@ -32732,28 +33434,40 @@
         <v>1649</v>
       </c>
       <c r="P226" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="Q226" t="s">
         <v>1650</v>
       </c>
       <c r="S226" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="T226" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="U226" s="26" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="V226" t="s">
         <v>1654</v>
       </c>
       <c r="W226" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="X226" t="s">
-        <v>2676</v>
+        <v>2677</v>
+      </c>
+      <c r="Y226" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z226" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA226" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB226" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC226">
         <v>43.425557699999999</v>
@@ -32797,22 +33511,25 @@
         <v>1650</v>
       </c>
       <c r="S227" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="T227" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="U227" s="27" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="V227" t="s">
         <v>1654</v>
       </c>
       <c r="W227" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="X227" t="s">
-        <v>2681</v>
+        <v>2682</v>
+      </c>
+      <c r="Y227" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z227" s="27" t="s">
         <v>1650</v>
@@ -32891,10 +33608,10 @@
         <v>1650</v>
       </c>
       <c r="S229" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="T229" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="U229" s="27" t="s">
         <v>1442</v>
@@ -32903,10 +33620,13 @@
         <v>1654</v>
       </c>
       <c r="W229" t="s">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="X229" t="s">
-        <v>2685</v>
+        <v>2686</v>
+      </c>
+      <c r="Y229" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z229" s="27" t="s">
         <v>1650</v>
@@ -32959,30 +33679,33 @@
         <v>1650</v>
       </c>
       <c r="S230" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="T230" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
       <c r="U230" s="26" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="V230" t="s">
         <v>1654</v>
       </c>
       <c r="W230" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="X230" t="s">
-        <v>2690</v>
-      </c>
-      <c r="Z230" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA230" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB230" s="26" t="s">
+        <v>2691</v>
+      </c>
+      <c r="Y230" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z230" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA230" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB230" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC230">
@@ -33027,22 +33750,25 @@
         <v>1650</v>
       </c>
       <c r="S231" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="T231" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="U231" s="27" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="V231" t="s">
         <v>1654</v>
       </c>
       <c r="W231" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="X231" t="s">
-        <v>2695</v>
+        <v>2696</v>
+      </c>
+      <c r="Y231" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z231" s="27" t="s">
         <v>1650</v>
@@ -33095,22 +33821,22 @@
         <v>1650</v>
       </c>
       <c r="S232" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="T232" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="U232" s="27" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="V232" t="s">
         <v>1654</v>
       </c>
       <c r="W232" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="X232" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="Y232" s="27" t="s">
         <v>1650</v>
@@ -33166,10 +33892,10 @@
         <v>1650</v>
       </c>
       <c r="S233" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="T233" t="s">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="U233" s="27" t="s">
         <v>1465</v>
@@ -33178,10 +33904,13 @@
         <v>1654</v>
       </c>
       <c r="W233" t="s">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="X233" t="s">
-        <v>2704</v>
+        <v>2705</v>
+      </c>
+      <c r="Y233" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z233" s="27" t="s">
         <v>1650</v>
@@ -33237,31 +33966,34 @@
         <v>1650</v>
       </c>
       <c r="S234" t="s">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="T234" t="s">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="U234" s="26" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="V234" t="s">
         <v>1654</v>
       </c>
       <c r="W234" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="X234" t="s">
-        <v>2709</v>
-      </c>
-      <c r="Y234" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="Z234" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA234" s="26" t="s">
-        <v>1650</v>
+        <v>2710</v>
+      </c>
+      <c r="Y234" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Z234" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA234" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB234" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC234">
         <v>29.821361199999991</v>
@@ -33305,22 +34037,25 @@
         <v>1650</v>
       </c>
       <c r="S235" t="s">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="T235" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="U235" s="27" t="s">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="V235" t="s">
         <v>1654</v>
       </c>
       <c r="W235" t="s">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="X235" t="s">
-        <v>2714</v>
+        <v>2715</v>
+      </c>
+      <c r="Y235" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z235" s="27" t="s">
         <v>1650</v>
@@ -33373,22 +34108,22 @@
         <v>1650</v>
       </c>
       <c r="S236" t="s">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="T236" t="s">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="U236" s="27" t="s">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="V236" t="s">
         <v>1654</v>
       </c>
       <c r="W236" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="X236" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="Y236" s="27" t="s">
         <v>1650</v>
@@ -33441,25 +34176,34 @@
         <v>1650</v>
       </c>
       <c r="S237" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="T237" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="U237" s="27" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="V237" t="s">
         <v>1654</v>
       </c>
       <c r="W237" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="X237" t="s">
-        <v>2724</v>
+        <v>2725</v>
+      </c>
+      <c r="Y237" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z237" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AA237" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB237" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC237">
         <v>41.0629487</v>
@@ -33503,22 +34247,25 @@
         <v>1650</v>
       </c>
       <c r="S238" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="T238" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="U238" s="27" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="V238" t="s">
         <v>1654</v>
       </c>
       <c r="W238" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="X238" t="s">
-        <v>2729</v>
+        <v>2730</v>
+      </c>
+      <c r="Y238" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z238" s="27" t="s">
         <v>1650</v>
@@ -33571,22 +34318,22 @@
         <v>1650</v>
       </c>
       <c r="S239" t="s">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="T239" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="U239" s="27" t="s">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="V239" t="s">
         <v>1654</v>
       </c>
       <c r="W239" t="s">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="X239" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="Y239" s="27" t="s">
         <v>1650</v>
@@ -33642,22 +34389,25 @@
         <v>1650</v>
       </c>
       <c r="S240" t="s">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="T240" t="s">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="U240" s="27" t="s">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="V240" t="s">
         <v>1654</v>
       </c>
       <c r="W240" t="s">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="X240" t="s">
-        <v>2739</v>
+        <v>2740</v>
+      </c>
+      <c r="Y240" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z240" s="27" t="s">
         <v>1650</v>
@@ -33710,25 +34460,28 @@
         <v>1650</v>
       </c>
       <c r="S241" t="s">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="T241" t="s">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="U241" s="27" t="s">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="V241" t="s">
         <v>1654</v>
       </c>
       <c r="W241" t="s">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="X241" t="s">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="Y241" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="Z241" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AA241" s="27" t="s">
         <v>1650</v>
@@ -33781,22 +34534,22 @@
         <v>1650</v>
       </c>
       <c r="S242" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="T242" t="s">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="U242" s="27" t="s">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="V242" t="s">
         <v>1654</v>
       </c>
       <c r="W242" t="s">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="X242" t="s">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="Y242" s="27" t="s">
         <v>1650</v>
@@ -33852,30 +34605,33 @@
         <v>1650</v>
       </c>
       <c r="S243" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="T243" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="U243" s="26" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="V243" t="s">
         <v>1654</v>
       </c>
       <c r="W243" t="s">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="X243" t="s">
-        <v>2754</v>
-      </c>
-      <c r="Z243" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA243" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB243" s="26" t="s">
+        <v>2755</v>
+      </c>
+      <c r="Y243" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z243" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA243" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB243" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC243">
@@ -33917,10 +34673,10 @@
         <v>1650</v>
       </c>
       <c r="S244" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="T244" t="s">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="U244" s="27" t="s">
         <v>1526</v>
@@ -33929,10 +34685,10 @@
         <v>1654</v>
       </c>
       <c r="W244" t="s">
-        <v>2757</v>
+        <v>2758</v>
       </c>
       <c r="X244" t="s">
-        <v>2758</v>
+        <v>2759</v>
       </c>
       <c r="Y244" s="27" t="s">
         <v>1650</v>
@@ -33988,28 +34744,34 @@
         <v>1650</v>
       </c>
       <c r="S245" t="s">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="T245" t="s">
-        <v>2760</v>
+        <v>2761</v>
       </c>
       <c r="U245" s="27" t="s">
-        <v>2761</v>
+        <v>2762</v>
       </c>
       <c r="V245" t="s">
         <v>1654</v>
       </c>
       <c r="W245" t="s">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="X245" t="s">
-        <v>2763</v>
+        <v>2764</v>
+      </c>
+      <c r="Y245" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z245" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA245" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB245" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC245">
         <v>35.054344800000003</v>
@@ -34053,22 +34815,22 @@
         <v>1650</v>
       </c>
       <c r="S246" t="s">
-        <v>2764</v>
+        <v>2765</v>
       </c>
       <c r="T246" t="s">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="U246" s="27" t="s">
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="V246" t="s">
         <v>1654</v>
       </c>
       <c r="W246" t="s">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="X246" t="s">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="Y246" s="27" t="s">
         <v>1650</v>
@@ -34124,22 +34886,22 @@
         <v>1650</v>
       </c>
       <c r="S247" t="s">
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="T247" t="s">
-        <v>2770</v>
+        <v>2771</v>
       </c>
       <c r="U247" s="27" t="s">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="V247" t="s">
         <v>1654</v>
       </c>
       <c r="W247" t="s">
-        <v>2772</v>
+        <v>2773</v>
       </c>
       <c r="X247" t="s">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="Y247" s="27" t="s">
         <v>1650</v>
@@ -34195,30 +34957,33 @@
         <v>1650</v>
       </c>
       <c r="S248" t="s">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="T248" t="s">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="U248" s="26" t="s">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="V248" t="s">
         <v>1654</v>
       </c>
       <c r="W248" t="s">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="X248" t="s">
-        <v>2778</v>
-      </c>
-      <c r="Z248" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA248" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AB248" s="26" t="s">
+        <v>2779</v>
+      </c>
+      <c r="Y248" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z248" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA248" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB248" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AC248">
@@ -34254,13 +35019,13 @@
         <v>1557</v>
       </c>
       <c r="N249" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="P249" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="S249" t="s">
-        <v>2779</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="250" spans="1:30">
@@ -34298,22 +35063,25 @@
         <v>1650</v>
       </c>
       <c r="S250" t="s">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="T250" t="s">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="U250" s="27" t="s">
-        <v>2782</v>
+        <v>2783</v>
       </c>
       <c r="V250" t="s">
         <v>1654</v>
       </c>
       <c r="W250" t="s">
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="X250" t="s">
-        <v>2784</v>
+        <v>2785</v>
+      </c>
+      <c r="Y250" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z250" s="27" t="s">
         <v>1650</v>
@@ -34363,22 +35131,25 @@
         <v>1650</v>
       </c>
       <c r="S251" t="s">
-        <v>2785</v>
+        <v>2786</v>
       </c>
       <c r="T251" t="s">
-        <v>2786</v>
+        <v>2787</v>
       </c>
       <c r="U251" s="27" t="s">
-        <v>2787</v>
+        <v>2788</v>
       </c>
       <c r="V251" t="s">
         <v>1654</v>
       </c>
       <c r="W251" t="s">
-        <v>2788</v>
+        <v>2789</v>
       </c>
       <c r="X251" t="s">
-        <v>2789</v>
+        <v>2790</v>
+      </c>
+      <c r="Y251" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z251" s="27" t="s">
         <v>1650</v>
@@ -34431,22 +35202,34 @@
         <v>1650</v>
       </c>
       <c r="S252" t="s">
-        <v>2790</v>
+        <v>2791</v>
       </c>
       <c r="T252" t="s">
-        <v>2791</v>
+        <v>2792</v>
       </c>
       <c r="U252" s="27" t="s">
-        <v>2792</v>
+        <v>2793</v>
       </c>
       <c r="V252" t="s">
         <v>1654</v>
       </c>
       <c r="W252" t="s">
-        <v>2793</v>
+        <v>2794</v>
       </c>
       <c r="X252" t="s">
-        <v>2794</v>
+        <v>2795</v>
+      </c>
+      <c r="Y252" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z252" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA252" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB252" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC252">
         <v>45.138161599999997</v>
@@ -34487,28 +35270,34 @@
         <v>1650</v>
       </c>
       <c r="S253" t="s">
-        <v>2795</v>
+        <v>2796</v>
       </c>
       <c r="T253" t="s">
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="U253" s="26" t="s">
-        <v>2797</v>
+        <v>2798</v>
       </c>
       <c r="V253" t="s">
         <v>1654</v>
       </c>
       <c r="W253" t="s">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="X253" t="s">
-        <v>2799</v>
-      </c>
-      <c r="Z253" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA253" s="26" t="s">
-        <v>1650</v>
+        <v>2800</v>
+      </c>
+      <c r="Y253" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z253" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA253" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB253" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC253">
         <v>43.994288699999998</v>
@@ -34552,28 +35341,34 @@
         <v>1650</v>
       </c>
       <c r="S254" t="s">
-        <v>2800</v>
+        <v>2801</v>
       </c>
       <c r="T254" t="s">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="U254" s="27" t="s">
-        <v>2802</v>
+        <v>2803</v>
       </c>
       <c r="V254" t="s">
         <v>1654</v>
       </c>
       <c r="W254" t="s">
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="X254" t="s">
-        <v>2804</v>
+        <v>2805</v>
+      </c>
+      <c r="Y254" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z254" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA254" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB254" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC254">
         <v>39.695586999999989</v>
@@ -34617,22 +35412,34 @@
         <v>1650</v>
       </c>
       <c r="S255" t="s">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="T255" t="s">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="U255" s="27" t="s">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="V255" t="s">
         <v>1654</v>
       </c>
       <c r="W255" t="s">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="X255" t="s">
-        <v>2809</v>
+        <v>2810</v>
+      </c>
+      <c r="Y255" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z255" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA255" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB255" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC255">
         <v>29.0212225</v>
@@ -34676,28 +35483,34 @@
         <v>1650</v>
       </c>
       <c r="S256" t="s">
-        <v>2810</v>
+        <v>2811</v>
       </c>
       <c r="T256" t="s">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="U256" s="26" t="s">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="V256" t="s">
         <v>1654</v>
       </c>
       <c r="W256" t="s">
-        <v>2813</v>
+        <v>2814</v>
       </c>
       <c r="X256" t="s">
-        <v>2814</v>
-      </c>
-      <c r="Z256" s="26" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AA256" s="26" t="s">
-        <v>1650</v>
+        <v>2815</v>
+      </c>
+      <c r="Y256" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z256" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AA256" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AB256" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC256">
         <v>27.982004199999999</v>
@@ -34741,22 +35554,25 @@
         <v>1650</v>
       </c>
       <c r="S257" t="s">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="T257" t="s">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="U257" s="27" t="s">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="V257" t="s">
         <v>1654</v>
       </c>
       <c r="W257" t="s">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="X257" t="s">
-        <v>2819</v>
+        <v>2820</v>
+      </c>
+      <c r="Y257" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z257" s="27" t="s">
         <v>1650</v>
@@ -34806,22 +35622,34 @@
         <v>1650</v>
       </c>
       <c r="S258" t="s">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="T258" t="s">
-        <v>2821</v>
+        <v>2822</v>
       </c>
       <c r="U258" s="27" t="s">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="V258" t="s">
         <v>1654</v>
       </c>
       <c r="W258" t="s">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="X258" t="s">
-        <v>2824</v>
+        <v>2825</v>
+      </c>
+      <c r="Y258" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z258" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA258" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB258" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC258">
         <v>33.691646000000013</v>
@@ -34865,10 +35693,10 @@
         <v>1650</v>
       </c>
       <c r="S259" t="s">
-        <v>2825</v>
+        <v>2826</v>
       </c>
       <c r="T259" t="s">
-        <v>2826</v>
+        <v>2827</v>
       </c>
       <c r="U259" s="27" t="s">
         <v>1604</v>
@@ -34877,16 +35705,22 @@
         <v>1654</v>
       </c>
       <c r="W259" t="s">
-        <v>2827</v>
+        <v>2828</v>
       </c>
       <c r="X259" t="s">
-        <v>2828</v>
+        <v>2829</v>
+      </c>
+      <c r="Y259" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z259" s="27" t="s">
         <v>1650</v>
       </c>
       <c r="AA259" s="27" t="s">
         <v>1650</v>
+      </c>
+      <c r="AB259" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC259">
         <v>64.80876529999999</v>
@@ -34930,22 +35764,34 @@
         <v>1650</v>
       </c>
       <c r="S260" t="s">
-        <v>2829</v>
+        <v>2830</v>
       </c>
       <c r="T260" t="s">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="U260" s="26" t="s">
-        <v>2831</v>
+        <v>2832</v>
       </c>
       <c r="V260" t="s">
         <v>1654</v>
       </c>
       <c r="W260" t="s">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="X260" t="s">
-        <v>2833</v>
+        <v>2834</v>
+      </c>
+      <c r="Y260" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="Z260" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AA260" s="26" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB260" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="AC260">
         <v>36.083999800000001</v>
@@ -34986,22 +35832,25 @@
         <v>1650</v>
       </c>
       <c r="S261" t="s">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="T261" t="s">
-        <v>2835</v>
+        <v>2836</v>
       </c>
       <c r="U261" s="27" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="V261" t="s">
         <v>1654</v>
       </c>
       <c r="W261" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="X261" t="s">
-        <v>2838</v>
+        <v>2839</v>
+      </c>
+      <c r="Y261" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z261" s="27" t="s">
         <v>1650</v>
@@ -35057,10 +35906,10 @@
         <v>1650</v>
       </c>
       <c r="S262" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="T262" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="U262" s="27" t="s">
         <v>1620</v>
@@ -35069,10 +35918,13 @@
         <v>1654</v>
       </c>
       <c r="W262" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="X262" t="s">
-        <v>2842</v>
+        <v>2843</v>
+      </c>
+      <c r="Y262" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z262" s="27" t="s">
         <v>1650</v>
@@ -35125,22 +35977,25 @@
         <v>1650</v>
       </c>
       <c r="S263" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="T263" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="U263" s="27" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="V263" t="s">
         <v>1654</v>
       </c>
       <c r="W263" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="X263" t="s">
-        <v>2847</v>
+        <v>2848</v>
+      </c>
+      <c r="Y263" s="26" t="s">
+        <v>1667</v>
       </c>
       <c r="Z263" s="27" t="s">
         <v>1650</v>
